--- a/2022 data/excel_outputs/116_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/116_boothwise_data.xlsx
@@ -14,933 +14,1485 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="515">
   <si>
     <t>AC 116 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
+    <t>Unnamed: 22</t>
+  </si>
+  <si>
+    <t>Unnamed: 23</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
     <t>POLLING STATION NAME</t>
   </si>
   <si>
-    <t>####0 ######## ##### #0 ##0 1</t>
-  </si>
-  <si>
-    <t>####0 ######## ###### #0 ##01</t>
-  </si>
-  <si>
-    <t>####0 ######## #### ###### #0 ##01</t>
-  </si>
-  <si>
-    <t>####0 ######## #### ###### #0 ##0 2</t>
-  </si>
-  <si>
-    <t>###### ### ######### ###### ##### ##### ###### #0##10</t>
-  </si>
-  <si>
-    <t>###### ### ######### ###### ##### ##### ###### #0##015</t>
-  </si>
-  <si>
-    <t>###### ### ######### ###### ##### ##### ###### #0##018</t>
-  </si>
-  <si>
-    <t>####0 ######## #### #### ###### ### #0##01</t>
-  </si>
-  <si>
-    <t>####0 ######## #### #### ###### ### #0##02</t>
-  </si>
-  <si>
-    <t>####0 ######## #### #### ####### ### #0##03</t>
-  </si>
-  <si>
-    <t>####0 ######## #### #### ####### ### #0##04</t>
-  </si>
-  <si>
-    <t>####0 ######## ######### #0 ##01</t>
-  </si>
-  <si>
-    <t>####0 ######## ######### #0 ##02</t>
-  </si>
-  <si>
-    <t>####0 ######## ##### #0 ####### #0 ##01</t>
-  </si>
-  <si>
-    <t>####0 ######## ####### ###### ### #0##01</t>
-  </si>
-  <si>
-    <t>####0 ######## ####### ###### ### #0##02</t>
-  </si>
-  <si>
-    <t>####0 ######## ####### ###0 #### ####### ### #0##01</t>
-  </si>
-  <si>
-    <t>####0 ######## ####### ###0 #### ####### ### #0##02</t>
-  </si>
-  <si>
-    <t>####0 ######## ####### ####### ### ### ### #0##01</t>
-  </si>
-  <si>
-    <t>####0 ######## ####### ####### ### ### ### #0##02</t>
-  </si>
-  <si>
-    <t>##### ###### ### ##### #######e ###### ### ##0 ##0 1</t>
-  </si>
-  <si>
-    <t>##### ###### ### ##### #######e ###### ### ##0 ##0 2</t>
-  </si>
-  <si>
-    <t>##### ###### ### ##### #######e ####### ### ##0 ##0 3</t>
-  </si>
-  <si>
-    <t>##### ###### ### ##### #######e ####### ### ##0 ##0 4</t>
-  </si>
-  <si>
-    <t>###### ######## ####### ###### ### #0##01</t>
-  </si>
-  <si>
-    <t>###### ######## ####### ###### ### #0##02</t>
-  </si>
-  <si>
-    <t>###### ######## ####### ####### ### #0##03</t>
-  </si>
-  <si>
-    <t>###### ######## ####### ####### ### #0##04</t>
-  </si>
-  <si>
-    <t>####0 ######## ########## ### #0 ##01</t>
-  </si>
-  <si>
-    <t>####0 ######## ###### #0##01</t>
-  </si>
-  <si>
-    <t>####0 ######## ###### #0##02</t>
-  </si>
-  <si>
-    <t>####0 ######## ###### ######## #0 ##01</t>
-  </si>
-  <si>
-    <t>####0 ######## ##### #0##01</t>
-  </si>
-  <si>
-    <t>####0 ######## ##### #0##02</t>
-  </si>
-  <si>
-    <t>###### ######## ##### ###### ### #0##01</t>
-  </si>
-  <si>
-    <t>###### ######## ##### ###### ### #0##02</t>
-  </si>
-  <si>
-    <t>###### ######## ##### ####### ### #0##03</t>
-  </si>
-  <si>
-    <t>####0 ######## ##### #0 ##01</t>
-  </si>
-  <si>
-    <t>####0 ######## ##### #0 ##02</t>
-  </si>
-  <si>
-    <t>####0 ######## ### #0 ##01</t>
-  </si>
-  <si>
-    <t>####0 ######## ### ## #### #0 ##01</t>
-  </si>
-  <si>
-    <t>####0 ######## ######## #0 ##01</t>
-  </si>
-  <si>
-    <t>####0 ######## ####### #### ###### #0 ##01</t>
-  </si>
-  <si>
-    <t>####0 ######## ##### ###### #0##01</t>
-  </si>
-  <si>
-    <t>####0 ######## ######## #0##01</t>
-  </si>
-  <si>
-    <t>####0 ######## ######## ###### ### #0##02</t>
-  </si>
-  <si>
-    <t>####0 ######## ######## ###### ### #0##03</t>
-  </si>
-  <si>
-    <t>####0 ######## ######## ###### ### #0##04</t>
-  </si>
-  <si>
-    <t>####0 ######## ####### #0 ###### #0##01</t>
-  </si>
-  <si>
-    <t>####0 ######## ###### #### #0 ###### #0 ##01</t>
-  </si>
-  <si>
-    <t>###### ###### ######## ######## ##### ##### ###### ### #0##01</t>
-  </si>
-  <si>
-    <t>###### ###### ######## ######## ##### ##### ###### ### #0##02</t>
-  </si>
-  <si>
-    <t>###### ###### ######## ######## ##### ##### ####### ### #0##03</t>
-  </si>
-  <si>
-    <t>###### ###### ######## ######## ##### ##### ####### ### #0##04</t>
-  </si>
-  <si>
-    <t>####0 ######## ##### #### #0##01</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ######## #### ###### ###### #0##01</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ######## #### ###### ###### #0##02</t>
-  </si>
-  <si>
-    <t>####0 ######## #### ####### #0 ##01</t>
-  </si>
-  <si>
-    <t>####0 ######## ####### #0##01</t>
-  </si>
-  <si>
-    <t>####0 ######## ###### #0 ##02</t>
-  </si>
-  <si>
-    <t>####0 ######## ###### #0 ##0 1</t>
-  </si>
-  <si>
-    <t>####0 ######## #### #### #0 ##01</t>
-  </si>
-  <si>
-    <t>####0 ######## ####### #0 ##01</t>
-  </si>
-  <si>
-    <t>####0 ######## ########### #0##01</t>
-  </si>
-  <si>
-    <t>####0 ######## ########### #0##02</t>
-  </si>
-  <si>
-    <t>####0 ######## #### #0##01</t>
-  </si>
-  <si>
-    <t>####0 ######## #### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0 ######## #### #0 ##01</t>
-  </si>
-  <si>
-    <t>####0 ######## #### #0 ##02</t>
-  </si>
-  <si>
-    <t>####0 ######## ########## #0##01</t>
-  </si>
-  <si>
-    <t>####0 ######## ##### ###### #0 ##01</t>
-  </si>
-  <si>
-    <t>####0 ######## ######## ###### #0##01</t>
-  </si>
-  <si>
-    <t>##### #### #### ##### ##### ##### #### ##### ###### #0###3</t>
-  </si>
-  <si>
-    <t>##### #### #### ##### ##### ##### #### ##### ###### #0##04</t>
-  </si>
-  <si>
-    <t>##### #### #### ##### ##### ##### #### ##### ###### #0##0 5</t>
-  </si>
-  <si>
-    <t>###### ########### #### ##### ###### #0##01</t>
-  </si>
-  <si>
-    <t>###### ########### #### ##### ###### #0##02</t>
-  </si>
-  <si>
-    <t>###### ########### #### ##### ###### #0##03</t>
-  </si>
-  <si>
-    <t>###### ########### #### ##### ###### #0##04</t>
-  </si>
-  <si>
-    <t>###### ###### ##### ###### ### #0 ##0 1</t>
-  </si>
-  <si>
-    <t>###### ###### ##### ###### ### #0 ##0 2</t>
-  </si>
-  <si>
-    <t>###### ###### ##### ###### ### #0 ##0 3</t>
-  </si>
-  <si>
-    <t>###### ######## ######### #0##01</t>
-  </si>
-  <si>
-    <t>##### ### ##### ### #0 ##0 ######## ####### #0##01</t>
-  </si>
-  <si>
-    <t>##### ### ##### ### #0 ##0 ######## ####### #0##02</t>
-  </si>
-  <si>
-    <t>####0 ######## #### #### #0##01</t>
-  </si>
-  <si>
-    <t>###### ######## #### #0##01</t>
-  </si>
-  <si>
-    <t>###### ######## #### #0##02</t>
-  </si>
-  <si>
-    <t>######### ##### ##### ####### #0##01</t>
-  </si>
-  <si>
-    <t>######### ##### ##### ####### #0##02</t>
-  </si>
-  <si>
-    <t>######### ##### ##### ####### #0##03</t>
-  </si>
-  <si>
-    <t>######### ##### ##### ####### #0##04</t>
-  </si>
-  <si>
-    <t>###### ### ##### ##### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0 ######## ##### #0 ##### #0##01</t>
-  </si>
-  <si>
-    <t>####0 ######## ##### #### ##### #0 ##01</t>
-  </si>
-  <si>
-    <t>####0 ######## ##### #### ##### #0 ##02</t>
-  </si>
-  <si>
-    <t>###### ### ##### ####### #0##01</t>
-  </si>
-  <si>
-    <t>###### ### ##### ####### #0##02</t>
-  </si>
-  <si>
-    <t>###### ### ##### ####### #0##03</t>
-  </si>
-  <si>
-    <t>####0 ######## ####### #### ####### #0##01</t>
-  </si>
-  <si>
-    <t>####0 ######## ###### ### #0##01</t>
-  </si>
-  <si>
-    <t>####0 ######## #### ### #0##01</t>
-  </si>
-  <si>
-    <t>####0 ######## ###### #### ### ### #0##01</t>
-  </si>
-  <si>
-    <t>####0 ######## ###### #### ### ### #0##02</t>
-  </si>
-  <si>
-    <t>####0 ######## #### #0##02</t>
-  </si>
-  <si>
-    <t>####0 ######## ####### #0##02</t>
-  </si>
-  <si>
-    <t>####0 ######## ######## #### ####### #0##01</t>
-  </si>
-  <si>
-    <t>####0 ######## ######## #### ####### #0##02</t>
-  </si>
-  <si>
-    <t>####0 ######## ######### #0##01</t>
-  </si>
-  <si>
-    <t>####0 ######## ######### #0##02</t>
-  </si>
-  <si>
-    <t>####0 ######## ###### ##### #0##01</t>
-  </si>
-  <si>
-    <t>####0 ######## #### ### #0 ##01</t>
-  </si>
-  <si>
-    <t>####0 ######## ### ###### ### #0##01</t>
-  </si>
-  <si>
-    <t>####0 ######## ### ###### ### #0##02</t>
-  </si>
-  <si>
-    <t>####0 ######## ### ####### ### #0##03</t>
-  </si>
-  <si>
-    <t>###### ######## ### #0##01</t>
-  </si>
-  <si>
-    <t>###### ######## ### #0##02</t>
-  </si>
-  <si>
-    <t>###### ######## ### #0##03</t>
-  </si>
-  <si>
-    <t>####0 ######## ##### ### #0##01</t>
-  </si>
-  <si>
-    <t>####0 ######## ######## #0##02</t>
-  </si>
-  <si>
-    <t>####0 ######## #### ##### #0##01</t>
-  </si>
-  <si>
-    <t>###### ######## ###### ###### ### #0##01</t>
-  </si>
-  <si>
-    <t>###### ######## ###### ###### ### #0##02</t>
-  </si>
-  <si>
-    <t>###### ######## ###### ####### ### #0##03</t>
-  </si>
-  <si>
-    <t>######### ####### ##### ###### ### ##### ######</t>
-  </si>
-  <si>
-    <t>####0 ######## ###### #0##03</t>
-  </si>
-  <si>
-    <t>####0 ######## ###### #0##04</t>
-  </si>
-  <si>
-    <t>####0 ######## ###### ######### #### 1</t>
-  </si>
-  <si>
-    <t>##### ###### ### ##### ###### #0##01</t>
-  </si>
-  <si>
-    <t>##### ###### ### ##### ###### #0##02</t>
-  </si>
-  <si>
-    <t>### ###### ######## ###### ##0 ##0 1</t>
-  </si>
-  <si>
-    <t>### ###### ######## ###### ### ######</t>
-  </si>
-  <si>
-    <t>####0 ######## ###### ####### ## ####### ###</t>
-  </si>
-  <si>
-    <t>####0 ######## ###### ####### #0##01</t>
-  </si>
-  <si>
-    <t>####0 ######## ###### #### #0##01</t>
-  </si>
-  <si>
-    <t>####0 ######## #### #### ###### #0##01</t>
-  </si>
-  <si>
-    <t>####0 ######## ##### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0 ######## ###### ####### #0##02</t>
-  </si>
-  <si>
-    <t>####0 ######## ####### ###### #0##01</t>
-  </si>
-  <si>
-    <t>####0 ######## ####### ###### #0##02</t>
-  </si>
-  <si>
-    <t>####0 ######## ### ####### #0##01</t>
-  </si>
-  <si>
-    <t>####0 ######## ### ####### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0 ######## #### ############ #0##01</t>
-  </si>
-  <si>
-    <t>####0 ######## #### ############ #0##02</t>
-  </si>
-  <si>
-    <t>###### ######## ###### #0##01</t>
-  </si>
-  <si>
-    <t>###### ######## ###### #0##02</t>
-  </si>
-  <si>
-    <t>####0 ######## ## #### #0##01</t>
-  </si>
-  <si>
-    <t>####0 ######## ####### #### #0##01</t>
-  </si>
-  <si>
-    <t>####0 ######## ####### #### #0##02</t>
-  </si>
-  <si>
-    <t>####0 ######## ####### ##### #0##01</t>
-  </si>
-  <si>
-    <t>####0 ######## ###### ###### ### #0 ##01</t>
-  </si>
-  <si>
-    <t>####0 ######## ###### ###### ### #0 ##02</t>
-  </si>
-  <si>
-    <t>####0 ######## ###### ####### ### #0 ##03</t>
-  </si>
-  <si>
-    <t>####0 ######## ###### ######## ####</t>
-  </si>
-  <si>
-    <t>####0 ######## ###### #0 ##0 2</t>
-  </si>
-  <si>
-    <t>####0 ######## ########## #0 ##01</t>
-  </si>
-  <si>
-    <t>####0 ######## ########## #0 ##02</t>
-  </si>
-  <si>
-    <t>####0 ######## #### #### #### ########## #0##01</t>
-  </si>
-  <si>
-    <t>####0 ######## #### ######## #0##01</t>
-  </si>
-  <si>
-    <t>###### ######## ###### ####### #0##01</t>
-  </si>
-  <si>
-    <t>###### ######## ###### ####### #0##02</t>
-  </si>
-  <si>
-    <t>####0 ######## ####### #0 ##02</t>
-  </si>
-  <si>
-    <t>####0######## ##### ####### #0##02</t>
-  </si>
-  <si>
-    <t>####0 ######## ########## #0##0 2</t>
-  </si>
-  <si>
-    <t>###### ######## #### ######## #0##01</t>
-  </si>
-  <si>
-    <t>###### ######## #### ######## #0##02</t>
-  </si>
-  <si>
-    <t>###### ######## #### ######## #0##03</t>
-  </si>
-  <si>
-    <t>####0 ######## ###### ###### #0##01</t>
-  </si>
-  <si>
-    <t>####0 ######## ###### ###### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0 ######## ###### ###### #0##0 3</t>
-  </si>
-  <si>
-    <t>####0 ######## ###### #### ###### ###### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0 ######## ###### #### ###### ###### #0##0 2</t>
-  </si>
-  <si>
-    <t>###### ######## ######## ###### ### #0##01</t>
-  </si>
-  <si>
-    <t>###### ######## ######## ###### ### #0##02</t>
-  </si>
-  <si>
-    <t>###### ######## ######## ####### ###### ### #0##03</t>
-  </si>
-  <si>
-    <t>###### ######## ######## ####### ###### ### #0##04</t>
-  </si>
-  <si>
-    <t>###### ######## ######## ###### ####### ### #0##05</t>
-  </si>
-  <si>
-    <t>###### ######## ######## ###### ####### ### #0##06</t>
-  </si>
-  <si>
-    <t>####0 ######## ######## ##0 ##0 1</t>
-  </si>
-  <si>
-    <t>####0 ######## ####### ######### #0##01</t>
-  </si>
-  <si>
-    <t>####0 ######## ####### ######### #0##02</t>
-  </si>
-  <si>
-    <t>####0 ######## ###### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0 ######## ####### #0##0 2</t>
-  </si>
-  <si>
-    <t>###### ######## ######## ########### #0##01</t>
-  </si>
-  <si>
-    <t>###### ######## ######## ########### #0##02</t>
-  </si>
-  <si>
-    <t>####0 ######## ########## ### #0##01</t>
-  </si>
-  <si>
-    <t>####0 ######## ########## ### #0 ##02</t>
-  </si>
-  <si>
-    <t>####0 ######## ########## ### ####### ### ###0 ####</t>
-  </si>
-  <si>
-    <t>####0 ######## ########## #0##02</t>
-  </si>
-  <si>
-    <t>####0 ######## ########## #0##0 3</t>
-  </si>
-  <si>
-    <t>####0 ######## ###### ######## #0##01</t>
-  </si>
-  <si>
-    <t>####0 ######## ###### ######## #0##02</t>
-  </si>
-  <si>
-    <t>####0 ######## ###### #0 ##03</t>
-  </si>
-  <si>
-    <t>####0 ######## #### #0 ###### #0##01</t>
-  </si>
-  <si>
-    <t>####0 ######## #### #### #### ####### #0##01</t>
-  </si>
-  <si>
-    <t>####0 ######## ####### ######## ####</t>
-  </si>
-  <si>
-    <t>####0 ######## ###### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0 ######## ##### ###### #0##02</t>
-  </si>
-  <si>
-    <t>####0 ######## #### #### ##0 ##0 1</t>
-  </si>
-  <si>
-    <t>####0 ######## ### #### #### ##### ####### #0##01</t>
-  </si>
-  <si>
-    <t>####0 ######## ### #### #### ##### ####### #0##02</t>
-  </si>
-  <si>
-    <t>####0 ######## ###### #### #### ##### #0##01</t>
-  </si>
-  <si>
-    <t>####0 ######## ####### #### #0 ####### #### #0##01</t>
-  </si>
-  <si>
-    <t>####0 ######## ####### #### #0 ####### #### #0##02</t>
-  </si>
-  <si>
-    <t>####0 ######## #### #### #0 ########## #0##01</t>
-  </si>
-  <si>
-    <t>####0 ######## #### #### #0 ########## #0##02</t>
-  </si>
-  <si>
-    <t>####0 ######## ######### #### ########## #0##01</t>
-  </si>
-  <si>
-    <t>####0 ######## ######### #### ########## #0##02</t>
-  </si>
-  <si>
-    <t>####0 ######## #### #### #### ##### #0##01</t>
-  </si>
-  <si>
-    <t>####0 ######## ######## #### ##### #0 ##01</t>
-  </si>
-  <si>
-    <t>####0 ######## ###### ###### ### #0##01</t>
-  </si>
-  <si>
-    <t>####0 ######## ###### ###### ### #0##02</t>
-  </si>
-  <si>
-    <t>####0 ######## ###### ####### ### #0##0 3</t>
-  </si>
-  <si>
-    <t>###### ######## ###### #0##0 2</t>
-  </si>
-  <si>
-    <t>###### ######## ####### ###### ###e #0##01</t>
-  </si>
-  <si>
-    <t>###### ######## ####### ###### ###e #0##02</t>
-  </si>
-  <si>
-    <t>###### ######## ####### ####### ### #0##0 4</t>
-  </si>
-  <si>
-    <t>##### ####0 ######## ####### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0 ######## ###### ###### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0 ######## #### #### #0 ##### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0 ######## ##### #### ##### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0 ######## ##### ###### ### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0 ######## ##### ###### ### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0 ######## ##### ####### ### #0##0 3</t>
-  </si>
-  <si>
-    <t>####0 ######## ##### ######## ###### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0 ######## ####### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0 ######## ######## #0##0 1</t>
-  </si>
-  <si>
-    <t>####0 ######## ######## #0##0 2</t>
-  </si>
-  <si>
-    <t>####0 ######## #### ####### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0 ######## ### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0 ######## ##### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0 ######## ######### #0 ### ##### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0 ######## ######### #0 ### ##### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0 ######## ###### #### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0 ######## ###### ##### #0##0 1</t>
-  </si>
-  <si>
-    <t>### ###### ##### ##### ###### ####### ### ##0 ##0 1</t>
-  </si>
-  <si>
-    <t>### ###### ##### ##### ###### ####### ### ##0 ##0 2</t>
-  </si>
-  <si>
-    <t>### ###### ##### ##### ###### ####### ### ##0 ##0 3</t>
-  </si>
-  <si>
-    <t>### ###### ##### ##### ###### ####### ### ##0 ##0 4</t>
-  </si>
-  <si>
-    <t>### ###### ##### ##### ###### ###### ### #0##0 5</t>
-  </si>
-  <si>
-    <t>### ###### ##### ##### ###### ###### ### #0##0 6</t>
-  </si>
-  <si>
-    <t>### ###### ##### ##### ###### ###### ### #0##0 7</t>
-  </si>
-  <si>
-    <t>##nn##nn###### ##### ##### ###### #0##0 1</t>
-  </si>
-  <si>
-    <t>##nn##nn###### ##### ##### ###### #0##0 2</t>
-  </si>
-  <si>
-    <t>##nn##nn###### ##### ##### ###### #0##0 3</t>
-  </si>
-  <si>
-    <t>####### ##0 ##0 ###### ##### ###### ###### ### #0 ##0 1</t>
-  </si>
-  <si>
-    <t>####### ##0 ##0 ###### ##### ###### ###### ### #0 ##0 2</t>
-  </si>
-  <si>
-    <t>####### ##0 ##0 ###### ##### ###### ###### ### #0 ##0 3</t>
-  </si>
-  <si>
-    <t>####### ##0 ##0 ###### ##### ###### ###### ### #0 ##0 4</t>
-  </si>
-  <si>
-    <t>####### ##0 ##0 ###### ##### ###### ####### ### #0 ##0 5</t>
-  </si>
-  <si>
-    <t>####### ##0 ##0 ###### ##### ###### ####### ### #0 ##0 6</t>
-  </si>
-  <si>
-    <t>##### ###### ######## ###### #0##0 1</t>
-  </si>
-  <si>
-    <t>##### ###### ######## ###### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0 ######## ##### #### ###### ####### ### #0##0 1</t>
-  </si>
-  <si>
-    <t>#### #### ######## #### ######### ##### #0##0 1</t>
-  </si>
-  <si>
-    <t>#### #### ######## #### ######### ##### #0##0 2</t>
-  </si>
-  <si>
-    <t>#### #### ######## #### ######### ##### #0##0 3</t>
-  </si>
-  <si>
-    <t>#### #### ######## #### ######### ##### #0##0 4</t>
-  </si>
-  <si>
-    <t>####.#.## ######## ##### ##### ###### #0##0 1</t>
-  </si>
-  <si>
-    <t>####.#.## ######## ##### ##### ###### #0##0 2</t>
-  </si>
-  <si>
-    <t>####.#.## ######## ##### ##### ###### #0##0 3</t>
-  </si>
-  <si>
-    <t>####.#.## ######## ##### ##### ###### #0##0 4</t>
-  </si>
-  <si>
-    <t>####.#.## ######## ##### ##### ###### #0##0 5</t>
-  </si>
-  <si>
-    <t>####.#.## ######## ##### ##### ###### #0##0 6</t>
-  </si>
-  <si>
-    <t>####.#.## ######## ##### ##### ###### #0##0 7</t>
-  </si>
-  <si>
-    <t>####0 ######## ###### ##### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0 ######## ####### ####### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0 ######## ####### ####### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0 ######## ###### #### ###### #0##01</t>
-  </si>
-  <si>
-    <t>####0 ######## ####### ######## #0##01</t>
-  </si>
-  <si>
-    <t>####0 ######## ####### #### ###### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0 ######## ###### ###### ### ##0 ##0 1</t>
-  </si>
-  <si>
-    <t>####0 ######## ###### ###### ### ##0 ##0 2</t>
-  </si>
-  <si>
-    <t>####0 ######## ###### ####### ### ##0 ##0 3</t>
-  </si>
-  <si>
-    <t>####0 ######## ###### ####### ### #0##04</t>
-  </si>
-  <si>
-    <t>###### ######## ###### ###### ### ##0##01</t>
-  </si>
-  <si>
-    <t>###### ######## ###### ####### ### #0##02</t>
-  </si>
-  <si>
-    <t>###### ######## ###### ####### ### #0##0 4</t>
-  </si>
-  <si>
-    <t>####0 ######## #### #### ###### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0 ######## #### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0 ######## ###### #### ###### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0 ######## ###### ### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0 ######## ##### #### ###### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0 ######## ##### #### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0 ######## ####### #0##0 3</t>
-  </si>
-  <si>
-    <t>####0 ######## ### ###### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0 ######## ######## ######## ####</t>
-  </si>
-  <si>
-    <t>####0 ######## ######## ###### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0 ######## ######## ###### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0 ######## ######### ###### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0 ######## ######### ###### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0 ######## ###### ####### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0 ######## ###### ####### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0 ######## ### ## #### #### ####### ### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0 ######## ##### ###### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0 ######## ##### ######### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0 ######## ##### ######### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0 ######## ####### #### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0 ######## ####### #### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0 ######## ##### ###### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0 ######## ######### ##### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0 ######## ####### ##### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0 ######## ########## #0##0 1</t>
-  </si>
-  <si>
-    <t>####0 ######## ######## #### #0##0 1</t>
-  </si>
-  <si>
-    <t>###### ######## ####### #0##0 1</t>
-  </si>
-  <si>
-    <t>###### ######## ####### #0##0 2</t>
+    <t>A0 VADHALAY GURAI K0 NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY BADARAPARU K0 NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY LAU.DA BAHE .DI K0 NAM01</t>
+  </si>
+  <si>
+    <t>LALA CHOTE LAL RADHE YAM NAVAYUVAK I TAR KALEJ BADAYAMU K0NAM010</t>
+  </si>
+  <si>
+    <t>LALA CHOTE LAL RADHE YAM NAVAYUVAK I TAR KALEJ BADAYAMU K0NAM015</t>
+  </si>
+  <si>
+    <t>LALA CHOTE LAL RADHE YAM NAVAYUVAK I TAR KALEJ BADAYAMU K0NAM018</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY MIRA SARAY U#TAR% BHAG K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY MIRA SARAY U#TAR% BHAG K0NAM02</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY MIRA SARAY D'(NI BHAG K0NAM03</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY MIRA SARAY D'(NI BHAG K0NAM04</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY JAHAMNABAD K0 NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY JAHAMNABAD K0 NAM02</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY GH+CHA M0 MAUJAMAPARU K0 NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY SHEKHAP U RU U#TAR% BHAG K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY SHEKHAP U RU U#TAR% BHAG K0NAM02</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY SHEKHAP U RU A0T0 K( D'(NI BHAG K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY SHEKHAP U RU A0T0 K( D'(NI BHAG K0NAM02</t>
+  </si>
+  <si>
+    <t>K YA JU0NAYAR HAI1KUL SHEKHAP U RU K0NAM01</t>
+  </si>
+  <si>
+    <t>K YA JU0NAYAR HAI1KUL SHEKHAP U RU K0NAM02</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL SHEKHAPU RU PAV U 2 BHAG K0NAM01</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL SHEKHAPU RU PAV U 2 BHAG K0NAM02</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL SHEKHAPU RU PI CHAMI BHAG K0NAM03</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL SHEKHAPU RU PI CHAMI BHAG K0NAM04</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY SHEKHAP U RU NAYA BHAVAN PI CHAMI BHAG K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY SHEKHAP U RU NAYA BHAVAN PI CHAMI BHAG K0NAM02</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY RAH%MU4IN NAGAR K0 NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY NAUSHERA K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY NAUSHERA K0NAM02</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY GUNAURA BAIJADAPARU K0 NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY JAJAPARU A K0 NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY IJARAUL% K0 NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY GATHAUNA K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY GATHAUNA K0NAM02</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY GAMGAURA K0 NAM01</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL BASOMA U#TAR% BHAG K0NAM01</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL BASOMA U#TAR% BHAG K0NAM02</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL BASOMA D'(NI BHAG K0NAM03</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY ADHAUL% K0 NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY ADHAUL% K0 NAM02</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY NARAU K0 NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY ACHAURA K0 NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY VAR% KA NAGALA K0 NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY GADAURA K0 NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY KUADAMDA K0 NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY RAYAPARU K0 NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY RAYAPARU K0 NAM02</t>
+  </si>
+  <si>
+    <t>KL0 SHRAKL|SHRCH|JBH|THABHKL|PKL|AI THATHABHJCH|PKL|AIKL THATHABHS BBH AIBHT|KL AIBHTBBH0THATHABHKL|J~N01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY NANAKHE.DA K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY NANAKHE.DA U#TAR% BHAG K0NAM03</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY NANAKHE.DA U#TAR% BHAG K0NAM04</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY DHAURE RA K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY AMIRAGAMJ M0 DHAURE RA K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY LALUIYA NAGALA M0 LALUIYA K0 NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY B+DAR% K0 NAM01</t>
+  </si>
+  <si>
+    <t>RAMAKAL% U&lt;CHATAR MA=Y:MAK VADHALAY BHU.DA BHADARAUL PAV U 2 BHAG K0NAM01</t>
+  </si>
+  <si>
+    <t>RAMAKAL% U&lt;CHATAR MA=Y:MAK VADHALAY BHU.DA BHADARAUL PAV U 2 BHAG K0NAM02</t>
+  </si>
+  <si>
+    <t>RAMAKAL% U&lt;CHATAR MA=Y:MAK VADHALAY BHU.DA BHADARAUL PI CHAMI BHAG K0NAM03</t>
+  </si>
+  <si>
+    <t>RAMAKAL% U&lt;CHATAR MA=Y:MAK VADHALAY BHU.DA BHADARAUL PI CHAMI BHAG K0NAM04</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY TE:LAYA NAGALA MAJARA I &gt;AI K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY KURAKHE.DA K0NAM01</t>
+  </si>
+  <si>
+    <t>KL0 SHRAKL|SHRCH|JBH|THABHKL|PKL|AI |PTHABHJKL|BBHAIBHT|KL|THATHABHKL|SHRABBH KL THATHABHS BBH AIBHT|KL AIBHTBBH0THATHABHKL|J~N01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY MAJARA GAMGAVARAR K0 NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY BHAKORA K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY GH@TAYAR% K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY ABARAU0TAYA K0 NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY BAMANOSI K0 NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY PHULASI K0 NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY CHETU NAGALA K0 NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY SUK@TAYA0 K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY CHACU DAYA K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY PATAPARAGAMJ K0 NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY M:LAKAPARU K0 NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY PHATEHAPARU K0 NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY TEHARA K0 NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY VANAGAVAM K0 NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY RANAU K0 NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY NASADELAPARU K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY NASADELAPARU K0NAM02</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY DHAMEI K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY SARAKAF K0 NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY SARAKAF K0 NAM02</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY SAGJANI K0 NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY DAVARAI K0 NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY :SARASA K0 NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY MUJA@HADAPARU K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY P:LAYA MAH HAD% K0 NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY IPHAROJAPARU IKALAHAR% K0NAM01</t>
+  </si>
+  <si>
+    <t>KUVAR DKAM :SAMH VAI@DAK I TAR KALEJ NAGALA SHAKAJ BADAYAMU K0NAM03</t>
+  </si>
+  <si>
+    <t>KUVAR DKAM :SAMH VAI@DAK I TAR KALEJ NAGALA SHAKAJ BADAYAMU K0NAM04</t>
+  </si>
+  <si>
+    <t>RAJAKAFY MAHA VADHALAY AVAS VAKAS BADAYAMU K0NAM01</t>
+  </si>
+  <si>
+    <t>RAJAKAFY MAHA VADHALAY AVAS VAKAS BADAYAMU K0NAM02</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY PADAUA K0 NAM01</t>
+  </si>
+  <si>
+    <t>AR0DI0EM0 JANASEVA PINLAK 1KUL, ADASHAO KRRIQNANAGAR 0NAKAT MAMDI S:M0T BADAYAMU K0NAM0 1</t>
+  </si>
+  <si>
+    <t>AR0DI0EM0 JANASEVA PINLAK 1KUL, ADASHAO KRRIQNANAGAR 0NAKAT MAMDI S:M0T BADAYAMU K0NAM0 2</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY BUDHAVAI K0NAM01</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL MAELAHAPARU K0NAM01</t>
+  </si>
+  <si>
+    <t>JU0HA0 1KUL KARAU:LAYA K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY KATHARA KHAGEI K0NAM01</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL MACHALAI K0NAM01</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL MACHALAI K0NAM02</t>
+  </si>
+  <si>
+    <t>RAQS%Y I TAR KALEJ GULACDAYA K0NAM01</t>
+  </si>
+  <si>
+    <t>RAQS%Y I TAR KALEJ GULACDAYA K0NAM02</t>
+  </si>
+  <si>
+    <t>RAQS%Y I TAR KALEJ GULACDAYA K0NAM03</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY TGADHAUL K0 NAM01</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI 1KUL TGADHAUL K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY PUNAU M0 TGADHAUL K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY B.DA PARASURA MAJARA TGADHAUL K0 NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY KAMALAPARU K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY MAHORA K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY DPAPARU K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY SALEMAPARU K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY VAMANI K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY GURAGAMV K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY GURAGAMV K0NAM02</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY AL%PARU A MAJARA GURAGAMV K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY SU DAR NAGAR K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY DARA NAGAR K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY UKHAVRAYA RAHALU NAYA BHAVAN K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY UKHAVRAYA RAHALU NAYA BHAVAN K0NAM02</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY NAITHU K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY NAITHU K0NAM02</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY BIBIPARU K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY PHATEHAPARU K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY PACHATAUR K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY HARANATHAPARU UPHAO TALAGAMV K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY UNAULA K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY UNAULA K0NAM02</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY BACHU A NAGALA K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY JAKHEL% K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY I1LAMAGAMJ K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY KHARAKHOL% KHADU O K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY HAYAT NAGAR K0 NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY JAGAT U#TAR% BHAG K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY JAGAT U#TAR% BHAG K0NAM02</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY JAGAT PI CHAMI BHAG K0NAM03</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL JAGAT K0NAM01</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL JAGAT K0NAM02</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY BEHATA EMAN K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY ISAPARU K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY KUWDEL% K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY PATASA K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY PATASA K0NAM02</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY DALAVA SHAH%DA K0NAM01</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL BHASARARA PAV U 2 BHAG K0NAM01</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL BHASARARA PAV U 2 BHAG K0NAM02</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL BHASARARA PI CHAMI BHAG K0NAM03</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL BHASARARA PAVRASAR MAH I1THAT AMGANAVADI KE &gt;</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY KUPAR% K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY GUDHANI K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY SAKHANAMU K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY SAKHANAMU K0NAM02</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY SAKHANAMU K0NAM03</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY SAKHANAMU K0NAM04</t>
+  </si>
+  <si>
+    <t>K YA JU0NAYAR HAI 1KUL SAKHANAMU K0NAM01</t>
+  </si>
+  <si>
+    <t>K YA JU0NAYAR HAI 1KUL SAKHANAMU K0NAM02</t>
+  </si>
+  <si>
+    <t>NAGAR PAMCHAYAT KAYAOLAY SAKHANAMU</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY HASANAPARU HUVRAYAI NAV0N:MAOT BHAVAN</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY ASAPARU K0 NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY IKAR% K0 NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY IKAR% K0 NAM02</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY V:SAYANI K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY KHARAKHOL% BAJ U U GAO K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY KU DAN NAGALA K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY G:BHAYAI K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY G:BHAYAI K0NAM02</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY NAGALA MAJARA G:BHAYAI K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY KUTARAI K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY JH DAPARU K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY SURAJAPARU K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY UDAMAI K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY MANAPARU KULACHAURA K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY RASULAPARU ABALAHAR% K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY RASULAPARU ABALAHAR% K0NAM02</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY NARAU BAJ U UGAO K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY DAUR% 0NARAM#TAMAPARU K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY DAUR% 0NARAM#TAMAPARU K0NAM02</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY :SAMAVRAYA K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY UPARAI LA K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY UPARAI LA K0NAM02</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY MAI BACH U N K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY UGHAINI K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY UGHAINI K0NAM02</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY K@T NA VARACHAU K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY K@T NA VARACHAU K0NAM02</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY VARACHAU K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY VARACHAU K0NAM02</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY MUGARAO JARASI K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY KAL PAYA K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY GAURAMAI PAV U 2 BHAG K0 NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY GAURAMAI PAV U 2 BHAG K0 NAM02</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY GAURAMAI PI CHAMI BHAG K0 NAM03</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY GAURAMAI A0TAVRAYT K(</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY PASEI K0 NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY PASEI K0 NAM02</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY A TUIYA K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY SADATHE R K0 NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY BARATCHARAO K0 NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY BARATCHARAO K0 NAM02</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY PEMI NAGALA MAJARA BARATCHARAO K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY SAKAR% JAMGAL PAVU 2 BHAG K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY SAKAR% JAMGAL PAVU 2 BHAG K0NAM02</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY SAKAR% JAMGAL PI CHAMI BHAG K0NAM03</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY SAKAR% JAMGAL PI CHAMI BHAG K0NAM04</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY A@HARAVARA K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY A@HARAVARA K0NAM02</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY NAGALA TAZYADAPARU K0NAM01</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL BARU AO PHAR%DAPARU K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY PATAURA K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY 0NAJAMAPARU MAJARA SHEKHAP U RU K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY AELAPARU CHAMAR% K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY MAUSAMAPARU K0 NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY MAUSAMAPARU K0 NAM02</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY UKHAVRAYA BAKARAPARU K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY UKHARAYA BAKARAPARU K0NAM02</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY MAELAMAI K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY AKHATAMAI K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY CHILAPARU A K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY ASARASI K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY ASARASI K0NAM02</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY I1MAILAPARU K0NAM01</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL SAKAR% KA:SAMAPARU K0NAM01</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL SAKAR% KA:SAMAPARU K0NAM02</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY BHAD:SAYA BHAMUIYA K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY BHAD:SAYA BHAMUIYA K0NAM02</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY BHAMUIYA MAJARA BHAD:SAYA BHAMUIYA K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY BHADARAU:LAYA K0NAM01</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL RAMAJANAPARU PAVU 2 BHAG K0NAM01</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL RAMAJANAPARU PAVU 2 BHAG K0NAM02</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL RAMAJANAPARU PI CHAMI U#TAR% BHAG K0NAM03</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL RAMAJANAPARU PI CHAMI U#TAR% BHAG K0NAM05</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL RAMAJANAPARU PAVU 2 D'(NI BHAG K0NAM04</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL RAMAJANAPARU PAVU 2 D'(NI BHAG K0NAM06</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY RAMAJANAPARU K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY :Mढ़AUL% :MAJAOPARU K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY :Mढ़AUL% :MAJAOPARU K0NAM02</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY :SASAURA K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY LOHATHE R K0NAM01</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KU DEL% BADAE U LAGAMJ K0NAM01</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KU DEL% BADAE U LAGAMJ K0NAM02</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY BEHATAD\BAR NAGAR K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY BEHATAD\BAR NAGAR D'(NI BHAG A0T0 K(</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY BEHATAD\BAR NAGAR K0 NAM02</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY MUH\MADAGAMJ K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY MUH\MADAGAMJ K0NAM02</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY DHANUPARU A K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY BHOJAPARU NARAYANAPARU K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY NURAPARU K0 NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY NURAPARU K0 NAM02</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY KACHAURA K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY KACHAURA K0 NAM02</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY KAITH:U LAYA K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY CHAU.DERA K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY 0NAJAMAPARU MAJARA :Mढ़AUL% K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY NAGALA M0 :SASAIYA K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY ABACHAULA K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY 0NAJAMABAD K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY LALUA NAGALA MAJARA JALALAPARU K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY JALALAPARU K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY JALALAPARU K0NAM02</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY RE VA K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY 0NADHANAPARU A K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY SUKHAO K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY LAKHAPU RU A K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY KUढ़A SHAHAPARU K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY KUढ़A SHAHAPARU K0NAM02</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY KAUA NAGALA MAJARA G@DHAYA GAMGAVARAR K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY DAJ U ON NAGALA MAJARA BARAURA K0NAM01</t>
+  </si>
+  <si>
+    <t>KL0 SHRAKL|SHRCH|JBH|THABHKL|PKL|AI |PMJ~NAKL|THATHABH THATHABHKL|AIKL|PKL AIBHTBBH0THATHABHKL|J~N01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY JOR% NAGALA M0 SU &gt;AYAN K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY KADARAVA.DI MAJARA SU &gt;AYAN K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY KADARAVA.DI MAJARA SU &gt;AYAN K0NAM02</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY KASHI NAGALA MAJARA KAKODA K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY GAMGINAGALA MAJARA KAKODA K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY KAKO.DA PAV U 2 BHAG K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY KAKO.DA PAV U 2 BHAG K0NAM02</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY KAKO.DA PI CHAMI BHAG K0NAM0 3</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KAKO.DA K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY GARAU:LAYA MAJARA KAKO.DA K0 NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY :SAVAYA HA:MADAPARU K0NAM01</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADARACHAUK PAV U 2 BHAG, K0NAM01</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADARACHAUK PAV U 2 BHAG, K0NAM02</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADARACHAUK PI CHAMI BHAG K0NAM03</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADARACHAUK PI CHAMI BHAG K0NAM0 4</t>
+  </si>
+  <si>
+    <t>K YA A0 VADHALAY KADARACHAUK K0NAM0 1</t>
+  </si>
+  <si>
+    <t>KL0 SHRAKL|SHRCH|JBH|THABHKL|PKL|AI AIKL|J~NADYAIKL|THATHABHKL|SHRABBH THATHABHS BBH AIBHT|KL AIBHTBBH0THATHABHKL|J~N0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY RAI SI NAGALA M0 :SAMARA K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY :SAMARA MAJARA LABHAR% K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY LABHAR% K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY LABHAR% K0NAM0 2</t>
+  </si>
+  <si>
+    <t>K YA A0 VADHALAY LABHAR% K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY G@DHAYA MUTA:LAKA NURAPARU K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY TATARAPARU K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY MAMURAGAMJ K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY NAUL% PHATUABAD K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY BACHI K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY JHAMJHARAU K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY VAR%KHE.DA M0 BACHI JHAMJHARAU K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY I VAR% NAGALA K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY VAVRAYA DAMDA K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY CHAMDABARAI K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY GAURAMAI K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY GAURAMAI K0NAM0 2</t>
+  </si>
+  <si>
+    <t>NAGAR PA:LAKA I TAR KALEJ KAKARALA PAV U 2 BHAG K0NAM0 16</t>
+  </si>
+  <si>
+    <t>NAGAR PA:LAKA I TAR KALEJ KAKARALA PAV U 2 BHAG K0NAM0 15</t>
+  </si>
+  <si>
+    <t>NAGAR PA:LAKA I TAR KALEJ KAKARALA PAV U 2 BHAG K0NAM0 14</t>
+  </si>
+  <si>
+    <t>NAGAR PA:LAKA I TAR KALEJ KAKARALA PAV U 2 BHAG K0NAM0 13</t>
+  </si>
+  <si>
+    <t>NAGAR PA:LAKA I TAR KALEJ KAKARALA U#TAR% PAVU 2 BHAG K0NAM0 12</t>
+  </si>
+  <si>
+    <t>NAGAR PA:LAKA I TAR KALEJ KAKARALA U#TAR% PAVU 2 BHAG K0NAM0 11</t>
+  </si>
+  <si>
+    <t>NAGAR PA:LAKA I TAR KALEJ KAKARALA U#TAR% PAVU 2 BHAG K0NAM0 10</t>
+  </si>
+  <si>
+    <t>NAGAR PA:LAKA I TAR KALEJ KAKARALA U#TAR% PAVU 2 BHAG K0NAM0 9</t>
+  </si>
+  <si>
+    <t>NAGAR PA:LAKA I TAR KALEJ KAKARALA U#TAR% BHAG K0NAM0 8</t>
+  </si>
+  <si>
+    <t>NAGAR PA:LAKA I TAR KALEJ KAKARALA U#TAR% BHAG K0NAM0 7</t>
+  </si>
+  <si>
+    <t>K YA JU0NAYAR HAI1KUL KAKARALA K0NAM0 1</t>
+  </si>
+  <si>
+    <t>K YA JU0NAYAR HAI1KUL KAKARALA K0NAM0 2</t>
+  </si>
+  <si>
+    <t>NAGAR PA:LAKA I TAR KALEJ KAKARALA U#TAR% BHAG K0NAM0 6</t>
+  </si>
+  <si>
+    <t>NAGAR PA:LAKA I TAR KALEJ KAKARALA U#TAR% BHAG K0NAM0 5</t>
+  </si>
+  <si>
+    <t>NAGAR PA:LAKA I TAR KALEJ KAKARALA PI CHAMI BHAG K0NAM0 4</t>
+  </si>
+  <si>
+    <t>NAGAR PA:LAKA I TAR KALEJ KAKARALA PI CHAMI BHAG K0NAM0 3</t>
+  </si>
+  <si>
+    <t>NAGAR PA:LAKA I TAR KALEJ KAKARALA PI CHAMI BHAG K0NAM0 2</t>
+  </si>
+  <si>
+    <t>NAGAR PA:LAKA I TAR KALEJ KAKARALA PI CHAMI BHAG K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY P:U LAS CHAUKAF KAKARALA PI CHAMI BHAG K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY P:U LAS CHAUKAF KAKARALA PI CHAMI BHAG A0TAVRAYT K(</t>
+  </si>
+  <si>
+    <t>AJAD JU0NAYAR HAI1KUL KAKARALA PI CHAMI BHAG K0NAM0 7</t>
+  </si>
+  <si>
+    <t>AJAD JU0NAYAR HAI1KUL KAKARALA PI CHAMI BHAG K0NAM0 6</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY P:U LAS CHAUKAF KAKARALA PI CHAMI BHAG K0NAM0 3</t>
+  </si>
+  <si>
+    <t>AJAD JU0NAYAR HAI1KUL KAKARALA D'(NI BHAG K0NAM0 4</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY P:U LAS CHAUKAF KAKARALA PI CHAMI BHAG K0NAM0 2</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY P:U LAS CHAUKAF KAKARALA NAVIN K(</t>
+  </si>
+  <si>
+    <t>AJAD JU0NAYAR HAI1KUL D'(NI BHAG K0NAM0 3</t>
+  </si>
+  <si>
+    <t>AJAD JU0NAYAR HAI1KUL D'(NI BHAG K0NAM0 2</t>
+  </si>
+  <si>
+    <t>AJAD JU0NAYAR HAI1KUL D'(NI BHAG K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY PHAR%DAPARU K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY SAMJARAPARU K0NAM0 2</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY IMADAPARU K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY ATHARAO KU0NAYA K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY TCHATAURA DHANAURA K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY TCHATAURA DHANAURA K0NAM0 2</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY ^Y+TI DHAMAOPARU K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY ^Y+TI DHAMAOPARU K0NAM0 2</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY DPAMAI UPHAO RAMANAGAR K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY VASHUNAPARU % K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY CHAU.DERA :SHAKARAPARU K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY A:BHAYASA MAJARA \YAU K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY \YAU D'(NI K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY \YAU PAV U 2 K0NAM0 4</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY \YAU D'(NI K0NAM0 2</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL \YAU D'(NI BHAG K0NAM02</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY \YAU PAV U 2 K0NAM0 3</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL \YAU D'(NI BHAG K0NAM03</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL \YAU K0NAM01</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY ढ़KA MAJARA \YAU K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY TGAETAI YA K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY KOTHA K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY VASHARAT NAGAR K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY ABALAHAR% K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY ABALAHAR% K0NAM0 2</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY K@TAYA K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY NAVADA MAJARA ALAPARU K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY CH D% NAGALA K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY URAU:LAYA K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY URAU:LAYA K0NAM0 2</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY SAIDAPARU K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY GUढ़ANA K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY VAVAI BHATAPARU A K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY MASUDAPARU A K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY TARASURA K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY KAKARAUA K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY BHASU DARA K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY BHASU DARA K0NAM0 2</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY @DAYOVRAYA ASAGUNA K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY @DAYOVRAYA ASAGUNA K0NAM0 2</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY :MAJAOPARU ABACHAULA K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY :MAJAOPARU ABACHAULA K0NAM0 2</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY SARANAMAI K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY @TAKARA K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY @TAKARA K0NAM0 2</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY :MAJAOPARU A0TARAJ K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY NAUGAVAM NASIRANAGAR K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY NAUGAVAM NASIRANAGAR K0NAM0 2</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY KESHOPARU K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY KON KA NAGALA MAJARA @DAYOKAL% KHAM K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY AJARAU K0NAM0 1</t>
+  </si>
+  <si>
+    <t>KL0 SHRAKL|SHRCH|JBH|THABHKL|PKL|AI KBHAIBHT|KL|AIBHTBBH|KL|SHRATHABH THATHABHSDYABBH AIBHT|KL AIBHTBBH0THATHABHKL|J~N0 1</t>
+  </si>
+  <si>
+    <t>KL0 SHRAKL|SHRCH|JBH|THABHKL|PKL|AI KBHAIBHT|KL|AIBHTBBH|KL|BBH THATHABHSDYABBH AIBHT|KL AIBHTBBH0THATHABHKL|J~N0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY HARE WDI K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY G@DHAYA HARADOP_I K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY G@DHAYA HARADOP_I K0NAM0 2</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY RASULAPARU NAGALA K0NAM0 1</t>
+  </si>
+  <si>
+    <t>KL0 SHRAKL|SHRCH|JBH|THABHKL|PKL|AI DYACHKL|SHRAK |PTHABH THATHABHS BBH AIBHT|KL AIBHTBBH0THATHABHKL|J~N0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY :MAJAOPARU VAS T K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY AHAMADANAGAR VACHAURA K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY ASAMAYA RAPHATAPARU K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY LALOMAI K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY AYTUIYA KALAM K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY GHASANAGALA K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY BHUWDI K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0 VADHALAY MUGAVRAYA NAGALA K0NAM0 1</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 1</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM NO. 401</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM NO. 402</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM NO. 403</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM NO. 404</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM NO. 405</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM NO. 406</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 407</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 408</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 409</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 410</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 411</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 412</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 413</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 414</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 415</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 416</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 417</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 418</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 419</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 420</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 421</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 422</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 423</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 424</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 425</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 426</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 427</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 428</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 429</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 430</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 431</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 432</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 433</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 434</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 435</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 436</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 437</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 438</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 439</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 440</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 441</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 442</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 443</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 444</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 445</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 446</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 447</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 448</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 449</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 450</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 451</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 452</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 453</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 454</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 455</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 456</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 457</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 458</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 459</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 460</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 461</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 462</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 463</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 464</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 465</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 466</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 467</t>
+  </si>
+  <si>
+    <t>JU0NAYAR HAI1KUL KADAMANAGALA K0NAM0 2 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 468</t>
   </si>
   <si>
     <t>TOTAL ELECTORS</t>
@@ -1013,8 +1565,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1030,7 +1590,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1038,12 +1598,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1342,82 +1920,151 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:24">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:24">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>309</v>
+        <v>493</v>
       </c>
       <c r="D2" t="s">
-        <v>310</v>
+        <v>494</v>
       </c>
       <c r="E2" t="s">
-        <v>311</v>
+        <v>495</v>
       </c>
       <c r="F2" t="s">
-        <v>312</v>
+        <v>496</v>
       </c>
       <c r="G2" t="s">
-        <v>313</v>
+        <v>497</v>
       </c>
       <c r="H2" t="s">
-        <v>314</v>
+        <v>498</v>
       </c>
       <c r="I2" t="s">
-        <v>315</v>
+        <v>499</v>
       </c>
       <c r="J2" t="s">
-        <v>316</v>
+        <v>500</v>
       </c>
       <c r="K2" t="s">
-        <v>317</v>
+        <v>501</v>
       </c>
       <c r="L2" t="s">
-        <v>318</v>
+        <v>502</v>
       </c>
       <c r="M2" t="s">
-        <v>319</v>
+        <v>503</v>
       </c>
       <c r="N2" t="s">
-        <v>320</v>
+        <v>504</v>
       </c>
       <c r="O2" t="s">
-        <v>321</v>
+        <v>505</v>
       </c>
       <c r="P2" t="s">
-        <v>322</v>
+        <v>506</v>
       </c>
       <c r="Q2" t="s">
-        <v>323</v>
+        <v>507</v>
       </c>
       <c r="R2" t="s">
-        <v>324</v>
+        <v>508</v>
       </c>
       <c r="S2" t="s">
-        <v>325</v>
+        <v>509</v>
       </c>
       <c r="T2" t="s">
-        <v>326</v>
+        <v>510</v>
       </c>
       <c r="U2" t="s">
-        <v>327</v>
+        <v>511</v>
       </c>
       <c r="V2" t="s">
-        <v>328</v>
+        <v>512</v>
       </c>
       <c r="W2" t="s">
-        <v>329</v>
+        <v>513</v>
       </c>
       <c r="X2" t="s">
-        <v>330</v>
+        <v>514</v>
       </c>
     </row>
     <row r="3" spans="1:24">
@@ -1425,7 +2072,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="C3">
         <v>1087</v>
@@ -1499,7 +2146,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="C4">
         <v>443</v>
@@ -1573,7 +2220,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="C5">
         <v>712</v>
@@ -1647,7 +2294,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="C6">
         <v>619</v>
@@ -1721,7 +2368,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="C7">
         <v>1106</v>
@@ -1795,7 +2442,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="C8">
         <v>1197</v>
@@ -1869,7 +2516,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C9">
         <v>809</v>
@@ -1943,7 +2590,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="C10">
         <v>1167</v>
@@ -2017,7 +2664,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="C11">
         <v>1019</v>
@@ -2091,7 +2738,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="C12">
         <v>1006</v>
@@ -2165,7 +2812,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="C13">
         <v>975</v>
@@ -2239,7 +2886,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="C14">
         <v>1032</v>
@@ -2313,7 +2960,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="C15">
         <v>1106</v>
@@ -2387,7 +3034,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="C16">
         <v>478</v>
@@ -2461,7 +3108,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="C17">
         <v>1062</v>
@@ -2535,7 +3182,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="C18">
         <v>1083</v>
@@ -2609,7 +3256,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="C19">
         <v>1006</v>
@@ -2683,7 +3330,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="C20">
         <v>1049</v>
@@ -2757,7 +3404,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="C21">
         <v>1045</v>
@@ -2831,7 +3478,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="C22">
         <v>902</v>
@@ -2905,7 +3552,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="C23">
         <v>881</v>
@@ -2979,7 +3626,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="C24">
         <v>702</v>
@@ -3053,7 +3700,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="C25">
         <v>806</v>
@@ -3127,7 +3774,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C26">
         <v>764</v>
@@ -3201,7 +3848,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="C27">
         <v>1049</v>
@@ -3275,7 +3922,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="C28">
         <v>899</v>
@@ -3349,7 +3996,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="C29">
         <v>1195</v>
@@ -3423,7 +4070,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="C30">
         <v>927</v>
@@ -3497,7 +4144,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="C31">
         <v>840</v>
@@ -3571,7 +4218,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="C32">
         <v>1066</v>
@@ -3645,7 +4292,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="C33">
         <v>1067</v>
@@ -3719,7 +4366,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C34">
         <v>415</v>
@@ -3793,7 +4440,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="C35">
         <v>656</v>
@@ -3867,7 +4514,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>4</v>
+        <v>59</v>
       </c>
       <c r="C36">
         <v>741</v>
@@ -3941,7 +4588,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="C37">
         <v>757</v>
@@ -4015,7 +4662,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="C38">
         <v>785</v>
@@ -4089,7 +4736,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>4</v>
+        <v>62</v>
       </c>
       <c r="C39">
         <v>780</v>
@@ -4163,7 +4810,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="C40">
         <v>917</v>
@@ -4237,7 +4884,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="C41">
         <v>1034</v>
@@ -4311,7 +4958,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="C42">
         <v>1054</v>
@@ -4385,7 +5032,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="C43">
         <v>1037</v>
@@ -4459,7 +5106,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="C44">
         <v>1023</v>
@@ -4533,7 +5180,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="C45">
         <v>916</v>
@@ -4607,7 +5254,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="C46">
         <v>908</v>
@@ -4681,7 +5328,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="C47">
         <v>986</v>
@@ -4755,7 +5402,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="C48">
         <v>519</v>
@@ -4829,7 +5476,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="C49">
         <v>981</v>
@@ -4903,7 +5550,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>4</v>
+        <v>73</v>
       </c>
       <c r="C50">
         <v>1054</v>
@@ -4977,7 +5624,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="C51">
         <v>809</v>
@@ -5051,7 +5698,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="C52">
         <v>715</v>
@@ -5125,7 +5772,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="C53">
         <v>970</v>
@@ -5199,7 +5846,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="C54">
         <v>992</v>
@@ -5273,7 +5920,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="C55">
         <v>940</v>
@@ -5347,7 +5994,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="C56">
         <v>918</v>
@@ -5421,7 +6068,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="C57">
         <v>1053</v>
@@ -5495,7 +6142,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="C58">
         <v>780</v>
@@ -5569,7 +6216,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="C59">
         <v>483</v>
@@ -5643,7 +6290,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>4</v>
+        <v>83</v>
       </c>
       <c r="C60">
         <v>914</v>
@@ -5717,7 +6364,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="C61">
         <v>911</v>
@@ -5791,7 +6438,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="C62">
         <v>1116</v>
@@ -5865,7 +6512,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="C63">
         <v>885</v>
@@ -5939,7 +6586,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="C64">
         <v>946</v>
@@ -6013,7 +6660,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>57</v>
+        <v>88</v>
       </c>
       <c r="C65">
         <v>854</v>
@@ -6087,7 +6734,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="C66">
         <v>550</v>
@@ -6161,7 +6808,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="C67">
         <v>612</v>
@@ -6235,7 +6882,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>59</v>
+        <v>91</v>
       </c>
       <c r="C68">
         <v>612</v>
@@ -6309,7 +6956,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="C69">
         <v>1072</v>
@@ -6383,7 +7030,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>35</v>
+        <v>93</v>
       </c>
       <c r="C70">
         <v>778</v>
@@ -6457,7 +7104,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>36</v>
+        <v>94</v>
       </c>
       <c r="C71">
         <v>764</v>
@@ -6531,7 +7178,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="C72">
         <v>929</v>
@@ -6605,7 +7252,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>44</v>
+        <v>96</v>
       </c>
       <c r="C73">
         <v>443</v>
@@ -6679,7 +7326,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>4</v>
+        <v>97</v>
       </c>
       <c r="C74">
         <v>710</v>
@@ -6753,7 +7400,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="C75">
         <v>645</v>
@@ -6827,7 +7474,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="C76">
         <v>1031</v>
@@ -6901,7 +7548,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="C77">
         <v>295</v>
@@ -6975,7 +7622,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="C78">
         <v>566</v>
@@ -7049,7 +7696,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>61</v>
+        <v>102</v>
       </c>
       <c r="C79">
         <v>547</v>
@@ -7123,7 +7770,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>44</v>
+        <v>103</v>
       </c>
       <c r="C80">
         <v>627</v>
@@ -7197,7 +7844,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>65</v>
+        <v>104</v>
       </c>
       <c r="C81">
         <v>605</v>
@@ -7271,7 +7918,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>65</v>
+        <v>105</v>
       </c>
       <c r="C82">
         <v>1034</v>
@@ -7345,7 +7992,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>40</v>
+        <v>106</v>
       </c>
       <c r="C83">
         <v>970</v>
@@ -7419,7 +8066,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>4</v>
+        <v>107</v>
       </c>
       <c r="C84">
         <v>819</v>
@@ -7493,7 +8140,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>42</v>
+        <v>108</v>
       </c>
       <c r="C85">
         <v>1078</v>
@@ -7567,7 +8214,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>66</v>
+        <v>109</v>
       </c>
       <c r="C86">
         <v>933</v>
@@ -7641,7 +8288,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>67</v>
+        <v>110</v>
       </c>
       <c r="C87">
         <v>951</v>
@@ -7715,7 +8362,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>68</v>
+        <v>111</v>
       </c>
       <c r="C88">
         <v>720</v>
@@ -7789,7 +8436,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>69</v>
+        <v>112</v>
       </c>
       <c r="C89">
         <v>661</v>
@@ -7863,7 +8510,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>70</v>
+        <v>113</v>
       </c>
       <c r="C90">
         <v>917</v>
@@ -7937,7 +8584,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>71</v>
+        <v>114</v>
       </c>
       <c r="C91">
         <v>858</v>
@@ -8011,7 +8658,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>4</v>
+        <v>115</v>
       </c>
       <c r="C92">
         <v>884</v>
@@ -8085,7 +8732,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>70</v>
+        <v>116</v>
       </c>
       <c r="C93">
         <v>942</v>
@@ -8159,7 +8806,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>40</v>
+        <v>117</v>
       </c>
       <c r="C94">
         <v>730</v>
@@ -8233,7 +8880,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="C95">
         <v>738</v>
@@ -8307,7 +8954,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="C96">
         <v>960</v>
@@ -8381,7 +9028,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>74</v>
+        <v>120</v>
       </c>
       <c r="C97">
         <v>558</v>
@@ -8455,7 +9102,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>75</v>
+        <v>121</v>
       </c>
       <c r="C98">
         <v>888</v>
@@ -8529,7 +9176,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>76</v>
+        <v>122</v>
       </c>
       <c r="C99">
         <v>984</v>
@@ -8603,7 +9250,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>77</v>
+        <v>123</v>
       </c>
       <c r="C100">
         <v>794</v>
@@ -8677,7 +9324,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>78</v>
+        <v>124</v>
       </c>
       <c r="C101">
         <v>756</v>
@@ -8751,7 +9398,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>79</v>
+        <v>125</v>
       </c>
       <c r="C102">
         <v>815</v>
@@ -8825,7 +9472,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="C103">
         <v>797</v>
@@ -8899,7 +9546,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="C104">
         <v>795</v>
@@ -8973,7 +9620,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>40</v>
+        <v>128</v>
       </c>
       <c r="C105">
         <v>750</v>
@@ -9047,7 +9694,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>41</v>
+        <v>129</v>
       </c>
       <c r="C106">
         <v>756</v>
@@ -9121,7 +9768,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>82</v>
+        <v>130</v>
       </c>
       <c r="C107">
         <v>1190</v>
@@ -9195,7 +9842,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="C108">
         <v>545</v>
@@ -9269,7 +9916,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>84</v>
+        <v>132</v>
       </c>
       <c r="C109">
         <v>706</v>
@@ -9343,7 +9990,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>32</v>
+        <v>133</v>
       </c>
       <c r="C110">
         <v>1095</v>
@@ -9417,7 +10064,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>85</v>
+        <v>134</v>
       </c>
       <c r="C111">
         <v>1053</v>
@@ -9491,7 +10138,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>86</v>
+        <v>135</v>
       </c>
       <c r="C112">
         <v>625</v>
@@ -9565,7 +10212,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>87</v>
+        <v>136</v>
       </c>
       <c r="C113">
         <v>606</v>
@@ -9639,7 +10286,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>88</v>
+        <v>137</v>
       </c>
       <c r="C114">
         <v>1194</v>
@@ -9713,7 +10360,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>89</v>
+        <v>138</v>
       </c>
       <c r="C115">
         <v>1172</v>
@@ -9787,7 +10434,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>90</v>
+        <v>139</v>
       </c>
       <c r="C116">
         <v>1073</v>
@@ -9861,7 +10508,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>91</v>
+        <v>140</v>
       </c>
       <c r="C117">
         <v>1068</v>
@@ -9935,7 +10582,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>92</v>
+        <v>141</v>
       </c>
       <c r="C118">
         <v>1044</v>
@@ -10009,7 +10656,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>93</v>
+        <v>142</v>
       </c>
       <c r="C119">
         <v>1228</v>
@@ -10083,7 +10730,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>94</v>
+        <v>143</v>
       </c>
       <c r="C120">
         <v>1027</v>
@@ -10157,7 +10804,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>40</v>
+        <v>144</v>
       </c>
       <c r="C121">
         <v>810</v>
@@ -10231,7 +10878,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>41</v>
+        <v>145</v>
       </c>
       <c r="C122">
         <v>846</v>
@@ -10305,7 +10952,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>95</v>
+        <v>146</v>
       </c>
       <c r="C123">
         <v>722</v>
@@ -10379,7 +11026,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>96</v>
+        <v>147</v>
       </c>
       <c r="C124">
         <v>594</v>
@@ -10453,7 +11100,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>97</v>
+        <v>148</v>
       </c>
       <c r="C125">
         <v>692</v>
@@ -10527,7 +11174,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>98</v>
+        <v>149</v>
       </c>
       <c r="C126">
         <v>622</v>
@@ -10601,7 +11248,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>61</v>
+        <v>150</v>
       </c>
       <c r="C127">
         <v>547</v>
@@ -10675,7 +11322,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>35</v>
+        <v>151</v>
       </c>
       <c r="C128">
         <v>715</v>
@@ -10749,7 +11396,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>36</v>
+        <v>152</v>
       </c>
       <c r="C129">
         <v>634</v>
@@ -10823,7 +11470,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>32</v>
+        <v>153</v>
       </c>
       <c r="C130">
         <v>1084</v>
@@ -10897,7 +11544,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>61</v>
+        <v>154</v>
       </c>
       <c r="C131">
         <v>949</v>
@@ -10971,7 +11618,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>68</v>
+        <v>155</v>
       </c>
       <c r="C132">
         <v>613</v>
@@ -11045,7 +11692,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>99</v>
+        <v>156</v>
       </c>
       <c r="C133">
         <v>876</v>
@@ -11119,7 +11766,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>100</v>
+        <v>157</v>
       </c>
       <c r="C134">
         <v>887</v>
@@ -11193,7 +11840,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>101</v>
+        <v>158</v>
       </c>
       <c r="C135">
         <v>772</v>
@@ -11267,7 +11914,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>102</v>
+        <v>159</v>
       </c>
       <c r="C136">
         <v>521</v>
@@ -11341,7 +11988,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>103</v>
+        <v>160</v>
       </c>
       <c r="C137">
         <v>616</v>
@@ -11415,7 +12062,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>104</v>
+        <v>161</v>
       </c>
       <c r="C138">
         <v>1122</v>
@@ -11489,7 +12136,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>105</v>
+        <v>162</v>
       </c>
       <c r="C139">
         <v>1094</v>
@@ -11563,7 +12210,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>106</v>
+        <v>163</v>
       </c>
       <c r="C140">
         <v>1079</v>
@@ -11637,7 +12284,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>68</v>
+        <v>164</v>
       </c>
       <c r="C141">
         <v>1069</v>
@@ -11711,7 +12358,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>107</v>
+        <v>165</v>
       </c>
       <c r="C142">
         <v>959</v>
@@ -11785,7 +12432,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>61</v>
+        <v>166</v>
       </c>
       <c r="C143">
         <v>705</v>
@@ -11859,7 +12506,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>108</v>
+        <v>167</v>
       </c>
       <c r="C144">
         <v>620</v>
@@ -11933,7 +12580,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>61</v>
+        <v>168</v>
       </c>
       <c r="C145">
         <v>708</v>
@@ -12007,7 +12654,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>35</v>
+        <v>169</v>
       </c>
       <c r="C146">
         <v>732</v>
@@ -12081,7 +12728,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>109</v>
+        <v>170</v>
       </c>
       <c r="C147">
         <v>714</v>
@@ -12155,7 +12802,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>110</v>
+        <v>171</v>
       </c>
       <c r="C148">
         <v>703</v>
@@ -12229,7 +12876,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>35</v>
+        <v>172</v>
       </c>
       <c r="C149">
         <v>944</v>
@@ -12303,7 +12950,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>36</v>
+        <v>173</v>
       </c>
       <c r="C150">
         <v>1101</v>
@@ -12377,7 +13024,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>88</v>
+        <v>174</v>
       </c>
       <c r="C151">
         <v>540</v>
@@ -12451,7 +13098,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>35</v>
+        <v>175</v>
       </c>
       <c r="C152">
         <v>814</v>
@@ -12525,7 +13172,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>36</v>
+        <v>176</v>
       </c>
       <c r="C153">
         <v>816</v>
@@ -12599,7 +13246,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>111</v>
+        <v>177</v>
       </c>
       <c r="C154">
         <v>680</v>
@@ -12673,7 +13320,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>112</v>
+        <v>178</v>
       </c>
       <c r="C155">
         <v>639</v>
@@ -12747,7 +13394,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>113</v>
+        <v>179</v>
       </c>
       <c r="C156">
         <v>970</v>
@@ -12821,7 +13468,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>114</v>
+        <v>180</v>
       </c>
       <c r="C157">
         <v>349</v>
@@ -12895,7 +13542,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>115</v>
+        <v>181</v>
       </c>
       <c r="C158">
         <v>1023</v>
@@ -12969,7 +13616,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>116</v>
+        <v>182</v>
       </c>
       <c r="C159">
         <v>1120</v>
@@ -13043,7 +13690,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>117</v>
+        <v>183</v>
       </c>
       <c r="C160">
         <v>1175</v>
@@ -13117,7 +13764,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>118</v>
+        <v>184</v>
       </c>
       <c r="C161">
         <v>957</v>
@@ -13191,7 +13838,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>119</v>
+        <v>185</v>
       </c>
       <c r="C162">
         <v>987</v>
@@ -13265,7 +13912,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>120</v>
+        <v>186</v>
       </c>
       <c r="C163">
         <v>1082</v>
@@ -13339,7 +13986,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>121</v>
+        <v>187</v>
       </c>
       <c r="C164">
         <v>660</v>
@@ -13413,7 +14060,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>32</v>
+        <v>188</v>
       </c>
       <c r="C165">
         <v>606</v>
@@ -13487,7 +14134,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>47</v>
+        <v>189</v>
       </c>
       <c r="C166">
         <v>605</v>
@@ -13561,7 +14208,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>122</v>
+        <v>190</v>
       </c>
       <c r="C167">
         <v>739</v>
@@ -13635,7 +14282,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>68</v>
+        <v>191</v>
       </c>
       <c r="C168">
         <v>1071</v>
@@ -13709,7 +14356,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>107</v>
+        <v>192</v>
       </c>
       <c r="C169">
         <v>687</v>
@@ -13783,7 +14430,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>123</v>
+        <v>193</v>
       </c>
       <c r="C170">
         <v>417</v>
@@ -13857,7 +14504,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>124</v>
+        <v>194</v>
       </c>
       <c r="C171">
         <v>1031</v>
@@ -13931,7 +14578,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="C172">
         <v>961</v>
@@ -14005,7 +14652,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>126</v>
+        <v>195</v>
       </c>
       <c r="C173">
         <v>1010</v>
@@ -14079,7 +14726,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>127</v>
+        <v>196</v>
       </c>
       <c r="C174">
         <v>934</v>
@@ -14153,7 +14800,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>35</v>
+        <v>197</v>
       </c>
       <c r="C175">
         <v>869</v>
@@ -14227,7 +14874,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>35</v>
+        <v>198</v>
       </c>
       <c r="C176">
         <v>457</v>
@@ -14301,7 +14948,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>32</v>
+        <v>199</v>
       </c>
       <c r="C177">
         <v>1029</v>
@@ -14375,7 +15022,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>33</v>
+        <v>200</v>
       </c>
       <c r="C178">
         <v>998</v>
@@ -14449,7 +15096,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>128</v>
+        <v>201</v>
       </c>
       <c r="C179">
         <v>1046</v>
@@ -14523,7 +15170,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C180">
         <v>988</v>
@@ -14597,7 +15244,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>130</v>
+        <v>203</v>
       </c>
       <c r="C181">
         <v>764</v>
@@ -14671,7 +15318,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>131</v>
+        <v>204</v>
       </c>
       <c r="C182">
         <v>1085</v>
@@ -14745,7 +15392,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>132</v>
+        <v>205</v>
       </c>
       <c r="C183">
         <v>878</v>
@@ -14819,7 +15466,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>133</v>
+        <v>206</v>
       </c>
       <c r="C184">
         <v>689</v>
@@ -14893,7 +15540,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>134</v>
+        <v>207</v>
       </c>
       <c r="C185">
         <v>718</v>
@@ -14967,7 +15614,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>135</v>
+        <v>208</v>
       </c>
       <c r="C186">
         <v>820</v>
@@ -15041,7 +15688,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>40</v>
+        <v>209</v>
       </c>
       <c r="C187">
         <v>511</v>
@@ -15115,7 +15762,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>70</v>
+        <v>210</v>
       </c>
       <c r="C188">
         <v>1015</v>
@@ -15189,7 +15836,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>71</v>
+        <v>211</v>
       </c>
       <c r="C189">
         <v>1108</v>
@@ -15263,7 +15910,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>61</v>
+        <v>212</v>
       </c>
       <c r="C190">
         <v>648</v>
@@ -15337,7 +15984,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>108</v>
+        <v>213</v>
       </c>
       <c r="C191">
         <v>650</v>
@@ -15411,7 +16058,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>136</v>
+        <v>214</v>
       </c>
       <c r="C192">
         <v>601</v>
@@ -15485,7 +16132,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="C193">
         <v>437</v>
@@ -15559,7 +16206,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>32</v>
+        <v>216</v>
       </c>
       <c r="C194">
         <v>946</v>
@@ -15633,7 +16280,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>33</v>
+        <v>217</v>
       </c>
       <c r="C195">
         <v>896</v>
@@ -15707,7 +16354,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>138</v>
+        <v>218</v>
       </c>
       <c r="C196">
         <v>1122</v>
@@ -15781,7 +16428,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>35</v>
+        <v>219</v>
       </c>
       <c r="C197">
         <v>830</v>
@@ -15855,7 +16502,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>139</v>
+        <v>220</v>
       </c>
       <c r="C198">
         <v>713</v>
@@ -15929,7 +16576,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>61</v>
+        <v>221</v>
       </c>
       <c r="C199">
         <v>695</v>
@@ -16003,7 +16650,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>61</v>
+        <v>222</v>
       </c>
       <c r="C200">
         <v>663</v>
@@ -16077,7 +16724,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>61</v>
+        <v>223</v>
       </c>
       <c r="C201">
         <v>774</v>
@@ -16151,7 +16798,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>68</v>
+        <v>224</v>
       </c>
       <c r="C202">
         <v>721</v>
@@ -16225,7 +16872,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>136</v>
+        <v>225</v>
       </c>
       <c r="C203">
         <v>654</v>
@@ -16299,7 +16946,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>140</v>
+        <v>226</v>
       </c>
       <c r="C204">
         <v>714</v>
@@ -16373,7 +17020,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>141</v>
+        <v>227</v>
       </c>
       <c r="C205">
         <v>1255</v>
@@ -16447,7 +17094,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>142</v>
+        <v>228</v>
       </c>
       <c r="C206">
         <v>977</v>
@@ -16521,7 +17168,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>143</v>
+        <v>229</v>
       </c>
       <c r="C207">
         <v>795</v>
@@ -16595,7 +17242,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>144</v>
+        <v>230</v>
       </c>
       <c r="C208">
         <v>783</v>
@@ -16669,7 +17316,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>145</v>
+        <v>231</v>
       </c>
       <c r="C209">
         <v>816</v>
@@ -16743,7 +17390,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>146</v>
+        <v>232</v>
       </c>
       <c r="C210">
         <v>872</v>
@@ -16817,7 +17464,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>61</v>
+        <v>233</v>
       </c>
       <c r="C211">
         <v>1155</v>
@@ -16891,7 +17538,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>147</v>
+        <v>234</v>
       </c>
       <c r="C212">
         <v>1111</v>
@@ -16965,7 +17612,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>148</v>
+        <v>235</v>
       </c>
       <c r="C213">
         <v>994</v>
@@ -17039,7 +17686,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>149</v>
+        <v>236</v>
       </c>
       <c r="C214">
         <v>1135</v>
@@ -17113,7 +17760,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>35</v>
+        <v>237</v>
       </c>
       <c r="C215">
         <v>1040</v>
@@ -17187,7 +17834,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>36</v>
+        <v>238</v>
       </c>
       <c r="C216">
         <v>984</v>
@@ -17261,7 +17908,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>150</v>
+        <v>239</v>
       </c>
       <c r="C217">
         <v>890</v>
@@ -17335,7 +17982,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>151</v>
+        <v>240</v>
       </c>
       <c r="C218">
         <v>849</v>
@@ -17409,7 +18056,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>68</v>
+        <v>241</v>
       </c>
       <c r="C219">
         <v>920</v>
@@ -17483,7 +18130,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>107</v>
+        <v>242</v>
       </c>
       <c r="C220">
         <v>852</v>
@@ -17557,7 +18204,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>152</v>
+        <v>243</v>
       </c>
       <c r="C221">
         <v>1128</v>
@@ -17631,7 +18278,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>32</v>
+        <v>244</v>
       </c>
       <c r="C222">
         <v>615</v>
@@ -17705,7 +18352,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="C223">
         <v>983</v>
@@ -17779,7 +18426,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>154</v>
+        <v>246</v>
       </c>
       <c r="C224">
         <v>1029</v>
@@ -17853,7 +18500,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>155</v>
+        <v>247</v>
       </c>
       <c r="C225">
         <v>1091</v>
@@ -17927,7 +18574,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>156</v>
+        <v>248</v>
       </c>
       <c r="C226">
         <v>980</v>
@@ -18001,7 +18648,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>70</v>
+        <v>249</v>
       </c>
       <c r="C227">
         <v>748</v>
@@ -18075,7 +18722,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>71</v>
+        <v>250</v>
       </c>
       <c r="C228">
         <v>736</v>
@@ -18149,7 +18796,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>47</v>
+        <v>251</v>
       </c>
       <c r="C229">
         <v>834</v>
@@ -18223,7 +18870,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>4</v>
+        <v>252</v>
       </c>
       <c r="C230">
         <v>732</v>
@@ -18297,7 +18944,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>157</v>
+        <v>253</v>
       </c>
       <c r="C231">
         <v>699</v>
@@ -18371,7 +19018,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>158</v>
+        <v>254</v>
       </c>
       <c r="C232">
         <v>833</v>
@@ -18445,7 +19092,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>159</v>
+        <v>255</v>
       </c>
       <c r="C233">
         <v>1079</v>
@@ -18519,7 +19166,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>160</v>
+        <v>256</v>
       </c>
       <c r="C234">
         <v>736</v>
@@ -18593,7 +19240,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>10</v>
+        <v>257</v>
       </c>
       <c r="C235">
         <v>1069</v>
@@ -18667,7 +19314,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>11</v>
+        <v>258</v>
       </c>
       <c r="C236">
         <v>1026</v>
@@ -18741,7 +19388,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>12</v>
+        <v>259</v>
       </c>
       <c r="C237">
         <v>967</v>
@@ -18815,7 +19462,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>13</v>
+        <v>260</v>
       </c>
       <c r="C238">
         <v>850</v>
@@ -18889,7 +19536,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>47</v>
+        <v>261</v>
       </c>
       <c r="C239">
         <v>834</v>
@@ -18963,7 +19610,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>122</v>
+        <v>262</v>
       </c>
       <c r="C240">
         <v>893</v>
@@ -19037,7 +19684,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>161</v>
+        <v>263</v>
       </c>
       <c r="C241">
         <v>885</v>
@@ -19111,7 +19758,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>162</v>
+        <v>264</v>
       </c>
       <c r="C242">
         <v>730</v>
@@ -19185,7 +19832,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>163</v>
+        <v>265</v>
       </c>
       <c r="C243">
         <v>680</v>
@@ -19259,7 +19906,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>35</v>
+        <v>266</v>
       </c>
       <c r="C244">
         <v>978</v>
@@ -19333,7 +19980,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>109</v>
+        <v>267</v>
       </c>
       <c r="C245">
         <v>361</v>
@@ -19407,7 +20054,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>57</v>
+        <v>268</v>
       </c>
       <c r="C246">
         <v>1173</v>
@@ -19481,7 +20128,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>65</v>
+        <v>269</v>
       </c>
       <c r="C247">
         <v>889</v>
@@ -19555,7 +20202,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>164</v>
+        <v>270</v>
       </c>
       <c r="C248">
         <v>857</v>
@@ -19629,7 +20276,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>136</v>
+        <v>271</v>
       </c>
       <c r="C249">
         <v>1020</v>
@@ -19703,7 +20350,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
       <c r="C250">
         <v>827</v>
@@ -19777,7 +20424,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>61</v>
+        <v>273</v>
       </c>
       <c r="C251">
         <v>409</v>
@@ -19851,7 +20498,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>61</v>
+        <v>274</v>
       </c>
       <c r="C252">
         <v>799</v>
@@ -19925,7 +20572,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>32</v>
+        <v>275</v>
       </c>
       <c r="C253">
         <v>862</v>
@@ -19999,7 +20646,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>61</v>
+        <v>276</v>
       </c>
       <c r="C254">
         <v>466</v>
@@ -20073,7 +20720,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>32</v>
+        <v>277</v>
       </c>
       <c r="C255">
         <v>901</v>
@@ -20147,7 +20794,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>33</v>
+        <v>278</v>
       </c>
       <c r="C256">
         <v>852</v>
@@ -20221,7 +20868,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>72</v>
+        <v>279</v>
       </c>
       <c r="C257">
         <v>729</v>
@@ -20295,7 +20942,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>166</v>
+        <v>280</v>
       </c>
       <c r="C258">
         <v>670</v>
@@ -20369,7 +21016,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>167</v>
+        <v>281</v>
       </c>
       <c r="C259">
         <v>1110</v>
@@ -20443,7 +21090,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>168</v>
+        <v>282</v>
       </c>
       <c r="C260">
         <v>1063</v>
@@ -20517,7 +21164,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>169</v>
+        <v>283</v>
       </c>
       <c r="C261">
         <v>760</v>
@@ -20591,7 +21238,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>170</v>
+        <v>284</v>
       </c>
       <c r="C262">
         <v>783</v>
@@ -20665,7 +21312,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>171</v>
+        <v>285</v>
       </c>
       <c r="C263">
         <v>1062</v>
@@ -20739,7 +21386,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>172</v>
+        <v>286</v>
       </c>
       <c r="C264">
         <v>760</v>
@@ -20813,7 +21460,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>173</v>
+        <v>287</v>
       </c>
       <c r="C265">
         <v>634</v>
@@ -20887,7 +21534,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>174</v>
+        <v>288</v>
       </c>
       <c r="C266">
         <v>655</v>
@@ -20961,7 +21608,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>47</v>
+        <v>289</v>
       </c>
       <c r="C267">
         <v>630</v>
@@ -21035,7 +21682,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>175</v>
+        <v>290</v>
       </c>
       <c r="C268">
         <v>964</v>
@@ -21109,7 +21756,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>176</v>
+        <v>291</v>
       </c>
       <c r="C269">
         <v>1074</v>
@@ -21183,7 +21830,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>177</v>
+        <v>292</v>
       </c>
       <c r="C270">
         <v>888</v>
@@ -21257,7 +21904,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>178</v>
+        <v>293</v>
       </c>
       <c r="C271">
         <v>922</v>
@@ -21331,7 +21978,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>179</v>
+        <v>294</v>
       </c>
       <c r="C272">
         <v>865</v>
@@ -21405,7 +22052,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>180</v>
+        <v>295</v>
       </c>
       <c r="C273">
         <v>1011</v>
@@ -21479,7 +22126,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>47</v>
+        <v>296</v>
       </c>
       <c r="C274">
         <v>769</v>
@@ -21553,7 +22200,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>181</v>
+        <v>297</v>
       </c>
       <c r="C275">
         <v>750</v>
@@ -21627,7 +22274,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>182</v>
+        <v>298</v>
       </c>
       <c r="C276">
         <v>992</v>
@@ -21701,7 +22348,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>183</v>
+        <v>299</v>
       </c>
       <c r="C277">
         <v>553</v>
@@ -21775,7 +22422,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>184</v>
+        <v>300</v>
       </c>
       <c r="C278">
         <v>511</v>
@@ -21849,7 +22496,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>61</v>
+        <v>301</v>
       </c>
       <c r="C279">
         <v>717</v>
@@ -21923,7 +22570,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>185</v>
+        <v>302</v>
       </c>
       <c r="C280">
         <v>693</v>
@@ -21997,7 +22644,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>186</v>
+        <v>303</v>
       </c>
       <c r="C281">
         <v>1175</v>
@@ -22071,7 +22718,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>187</v>
+        <v>304</v>
       </c>
       <c r="C282">
         <v>1152</v>
@@ -22145,7 +22792,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>188</v>
+        <v>305</v>
       </c>
       <c r="C283">
         <v>906</v>
@@ -22219,7 +22866,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>189</v>
+        <v>306</v>
       </c>
       <c r="C284">
         <v>1175</v>
@@ -22293,7 +22940,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>190</v>
+        <v>307</v>
       </c>
       <c r="C285">
         <v>1120</v>
@@ -22367,7 +23014,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>72</v>
+        <v>308</v>
       </c>
       <c r="C286">
         <v>900</v>
@@ -22441,7 +23088,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>191</v>
+        <v>309</v>
       </c>
       <c r="C287">
         <v>701</v>
@@ -22515,7 +23162,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>192</v>
+        <v>310</v>
       </c>
       <c r="C288">
         <v>896</v>
@@ -22589,7 +23236,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>61</v>
+        <v>311</v>
       </c>
       <c r="C289">
         <v>655</v>
@@ -22663,7 +23310,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>108</v>
+        <v>312</v>
       </c>
       <c r="C290">
         <v>644</v>
@@ -22737,7 +23384,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>193</v>
+        <v>313</v>
       </c>
       <c r="C291">
         <v>628</v>
@@ -22811,7 +23458,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>194</v>
+        <v>314</v>
       </c>
       <c r="C292">
         <v>672</v>
@@ -22885,7 +23532,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>4</v>
+        <v>315</v>
       </c>
       <c r="C293">
         <v>791</v>
@@ -22959,7 +23606,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>62</v>
+        <v>316</v>
       </c>
       <c r="C294">
         <v>791</v>
@@ -23033,7 +23680,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>195</v>
+        <v>317</v>
       </c>
       <c r="C295">
         <v>858</v>
@@ -23107,7 +23754,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>35</v>
+        <v>318</v>
       </c>
       <c r="C296">
         <v>823</v>
@@ -23181,7 +23828,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>41</v>
+        <v>319</v>
       </c>
       <c r="C297">
         <v>726</v>
@@ -23255,7 +23902,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>184</v>
+        <v>320</v>
       </c>
       <c r="C298">
         <v>1092</v>
@@ -23329,7 +23976,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>61</v>
+        <v>321</v>
       </c>
       <c r="C299">
         <v>1172</v>
@@ -23403,7 +24050,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>109</v>
+        <v>322</v>
       </c>
       <c r="C300">
         <v>456</v>
@@ -23477,7 +24124,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>196</v>
+        <v>323</v>
       </c>
       <c r="C301">
         <v>680</v>
@@ -23551,7 +24198,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>32</v>
+        <v>324</v>
       </c>
       <c r="C302">
         <v>526</v>
@@ -23625,7 +24272,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>111</v>
+        <v>325</v>
       </c>
       <c r="C303">
         <v>1014</v>
@@ -23699,7 +24346,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>197</v>
+        <v>326</v>
       </c>
       <c r="C304">
         <v>1029</v>
@@ -23773,7 +24420,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>61</v>
+        <v>327</v>
       </c>
       <c r="C305">
         <v>1010</v>
@@ -23847,7 +24494,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>108</v>
+        <v>328</v>
       </c>
       <c r="C306">
         <v>1110</v>
@@ -23921,7 +24568,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>198</v>
+        <v>329</v>
       </c>
       <c r="C307">
         <v>856</v>
@@ -23995,7 +24642,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>68</v>
+        <v>330</v>
       </c>
       <c r="C308">
         <v>882</v>
@@ -24069,7 +24716,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>111</v>
+        <v>331</v>
       </c>
       <c r="C309">
         <v>796</v>
@@ -24143,7 +24790,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>32</v>
+        <v>332</v>
       </c>
       <c r="C310">
         <v>726</v>
@@ -24217,7 +24864,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>199</v>
+        <v>333</v>
       </c>
       <c r="C311">
         <v>724</v>
@@ -24291,7 +24938,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>61</v>
+        <v>334</v>
       </c>
       <c r="C312">
         <v>639</v>
@@ -24365,7 +25012,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>46</v>
+        <v>335</v>
       </c>
       <c r="C313">
         <v>983</v>
@@ -24439,7 +25086,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>200</v>
+        <v>336</v>
       </c>
       <c r="C314">
         <v>1016</v>
@@ -24513,7 +25160,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>201</v>
+        <v>337</v>
       </c>
       <c r="C315">
         <v>663</v>
@@ -24587,7 +25234,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>202</v>
+        <v>338</v>
       </c>
       <c r="C316">
         <v>701</v>
@@ -24661,7 +25308,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>203</v>
+        <v>339</v>
       </c>
       <c r="C317">
         <v>567</v>
@@ -24735,7 +25382,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>204</v>
+        <v>340</v>
       </c>
       <c r="C318">
         <v>738</v>
@@ -24809,7 +25456,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>205</v>
+        <v>341</v>
       </c>
       <c r="C319">
         <v>795</v>
@@ -24883,7 +25530,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>206</v>
+        <v>342</v>
       </c>
       <c r="C320">
         <v>577</v>
@@ -24957,7 +25604,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>207</v>
+        <v>343</v>
       </c>
       <c r="C321">
         <v>806</v>
@@ -25031,7 +25678,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>208</v>
+        <v>344</v>
       </c>
       <c r="C322">
         <v>779</v>
@@ -25105,7 +25752,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>209</v>
+        <v>345</v>
       </c>
       <c r="C323">
         <v>1164</v>
@@ -25179,7 +25826,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>210</v>
+        <v>346</v>
       </c>
       <c r="C324">
         <v>955</v>
@@ -25253,7 +25900,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>211</v>
+        <v>347</v>
       </c>
       <c r="C325">
         <v>1201</v>
@@ -25327,7 +25974,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>212</v>
+        <v>348</v>
       </c>
       <c r="C326">
         <v>1144</v>
@@ -25401,7 +26048,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>213</v>
+        <v>349</v>
       </c>
       <c r="C327">
         <v>1182</v>
@@ -25475,7 +26122,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>214</v>
+        <v>350</v>
       </c>
       <c r="C328">
         <v>1218</v>
@@ -25549,7 +26196,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>215</v>
+        <v>351</v>
       </c>
       <c r="C329">
         <v>1199</v>
@@ -25623,7 +26270,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>147</v>
+        <v>352</v>
       </c>
       <c r="C330">
         <v>731</v>
@@ -25697,7 +26344,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>216</v>
+        <v>353</v>
       </c>
       <c r="C331">
         <v>722</v>
@@ -25771,7 +26418,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>45</v>
+        <v>354</v>
       </c>
       <c r="C332">
         <v>805</v>
@@ -25845,7 +26492,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>193</v>
+        <v>355</v>
       </c>
       <c r="C333">
         <v>643</v>
@@ -25919,7 +26566,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>194</v>
+        <v>356</v>
       </c>
       <c r="C334">
         <v>619</v>
@@ -25993,7 +26640,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>217</v>
+        <v>357</v>
       </c>
       <c r="C335">
         <v>1175</v>
@@ -26067,7 +26714,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>218</v>
+        <v>358</v>
       </c>
       <c r="C336">
         <v>1000</v>
@@ -26141,7 +26788,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>29</v>
+        <v>359</v>
       </c>
       <c r="C337">
         <v>1016</v>
@@ -26215,7 +26862,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>219</v>
+        <v>360</v>
       </c>
       <c r="C338">
         <v>1071</v>
@@ -26289,7 +26936,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>220</v>
+        <v>361</v>
       </c>
       <c r="C339">
         <v>615</v>
@@ -26363,7 +27010,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>221</v>
+        <v>362</v>
       </c>
       <c r="C340">
         <v>386</v>
@@ -26437,7 +27084,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>222</v>
+        <v>363</v>
       </c>
       <c r="C341">
         <v>1012</v>
@@ -26511,7 +27158,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>223</v>
+        <v>364</v>
       </c>
       <c r="C342">
         <v>624</v>
@@ -26585,7 +27232,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>224</v>
+        <v>365</v>
       </c>
       <c r="C343">
         <v>1008</v>
@@ -26659,7 +27306,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>225</v>
+        <v>366</v>
       </c>
       <c r="C344">
         <v>1027</v>
@@ -26733,7 +27380,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>226</v>
+        <v>367</v>
       </c>
       <c r="C345">
         <v>1140</v>
@@ -26807,7 +27454,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>227</v>
+        <v>368</v>
       </c>
       <c r="C346">
         <v>577</v>
@@ -26881,7 +27528,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>228</v>
+        <v>369</v>
       </c>
       <c r="C347">
         <v>681</v>
@@ -26955,7 +27602,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>185</v>
+        <v>370</v>
       </c>
       <c r="C348">
         <v>643</v>
@@ -27029,7 +27676,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>229</v>
+        <v>371</v>
       </c>
       <c r="C349">
         <v>732</v>
@@ -27103,7 +27750,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>230</v>
+        <v>372</v>
       </c>
       <c r="C350">
         <v>702</v>
@@ -27177,7 +27824,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>231</v>
+        <v>373</v>
       </c>
       <c r="C351">
         <v>1084</v>
@@ -27251,7 +27898,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>232</v>
+        <v>374</v>
       </c>
       <c r="C352">
         <v>1041</v>
@@ -27325,7 +27972,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>233</v>
+        <v>375</v>
       </c>
       <c r="C353">
         <v>687</v>
@@ -27399,7 +28046,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>139</v>
+        <v>376</v>
       </c>
       <c r="C354">
         <v>646</v>
@@ -27473,7 +28120,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>234</v>
+        <v>377</v>
       </c>
       <c r="C355">
         <v>704</v>
@@ -27547,7 +28194,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>235</v>
+        <v>378</v>
       </c>
       <c r="C356">
         <v>685</v>
@@ -27621,7 +28268,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>236</v>
+        <v>379</v>
       </c>
       <c r="C357">
         <v>1066</v>
@@ -27695,7 +28342,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>237</v>
+        <v>380</v>
       </c>
       <c r="C358">
         <v>528</v>
@@ -27769,7 +28416,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>229</v>
+        <v>381</v>
       </c>
       <c r="C359">
         <v>573</v>
@@ -27843,7 +28490,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>184</v>
+        <v>382</v>
       </c>
       <c r="C360">
         <v>904</v>
@@ -27917,7 +28564,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>199</v>
+        <v>383</v>
       </c>
       <c r="C361">
         <v>934</v>
@@ -27991,7 +28638,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>238</v>
+        <v>384</v>
       </c>
       <c r="C362">
         <v>1201</v>
@@ -28065,7 +28712,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>239</v>
+        <v>385</v>
       </c>
       <c r="C363">
         <v>1157</v>
@@ -28139,7 +28786,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>240</v>
+        <v>386</v>
       </c>
       <c r="C364">
         <v>1097</v>
@@ -28213,7 +28860,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>241</v>
+        <v>387</v>
       </c>
       <c r="C365">
         <v>1108</v>
@@ -28287,7 +28934,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>242</v>
+        <v>388</v>
       </c>
       <c r="C366">
         <v>808</v>
@@ -28361,7 +29008,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>243</v>
+        <v>389</v>
       </c>
       <c r="C367">
         <v>934</v>
@@ -28435,7 +29082,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>244</v>
+        <v>390</v>
       </c>
       <c r="C368">
         <v>923</v>
@@ -28509,7 +29156,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>245</v>
+        <v>391</v>
       </c>
       <c r="C369">
         <v>1206</v>
@@ -28583,7 +29230,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>246</v>
+        <v>392</v>
       </c>
       <c r="C370">
         <v>767</v>
@@ -28657,7 +29304,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>247</v>
+        <v>393</v>
       </c>
       <c r="C371">
         <v>1158</v>
@@ -28731,7 +29378,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>248</v>
+        <v>394</v>
       </c>
       <c r="C372">
         <v>1174</v>
@@ -28805,7 +29452,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>249</v>
+        <v>395</v>
       </c>
       <c r="C373">
         <v>1060</v>
@@ -28879,7 +29526,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>250</v>
+        <v>396</v>
       </c>
       <c r="C374">
         <v>1072</v>
@@ -28953,7 +29600,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>251</v>
+        <v>397</v>
       </c>
       <c r="C375">
         <v>1154</v>
@@ -29027,7 +29674,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>252</v>
+        <v>398</v>
       </c>
       <c r="C376">
         <v>1139</v>
@@ -29101,7 +29748,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>253</v>
+        <v>399</v>
       </c>
       <c r="C377">
         <v>1140</v>
@@ -29175,7 +29822,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>254</v>
+        <v>400</v>
       </c>
       <c r="C378">
         <v>1168</v>
@@ -29249,7 +29896,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>255</v>
+        <v>401</v>
       </c>
       <c r="C379">
         <v>759</v>
@@ -29323,7 +29970,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>256</v>
+        <v>402</v>
       </c>
       <c r="C380">
         <v>1052</v>
@@ -29397,7 +30044,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>257</v>
+        <v>403</v>
       </c>
       <c r="C381">
         <v>1014</v>
@@ -29471,7 +30118,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>258</v>
+        <v>404</v>
       </c>
       <c r="C382">
         <v>1049</v>
@@ -29545,7 +30192,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>259</v>
+        <v>405</v>
       </c>
       <c r="C383">
         <v>1090</v>
@@ -29619,7 +30266,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>260</v>
+        <v>406</v>
       </c>
       <c r="C384">
         <v>1156</v>
@@ -29693,7 +30340,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>261</v>
+        <v>407</v>
       </c>
       <c r="C385">
         <v>1096</v>
@@ -29767,7 +30414,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>262</v>
+        <v>408</v>
       </c>
       <c r="C386">
         <v>1026</v>
@@ -29841,7 +30488,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>263</v>
+        <v>409</v>
       </c>
       <c r="C387">
         <v>929</v>
@@ -29915,7 +30562,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>264</v>
+        <v>410</v>
       </c>
       <c r="C388">
         <v>1197</v>
@@ -29989,7 +30636,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>265</v>
+        <v>411</v>
       </c>
       <c r="C389">
         <v>1042</v>
@@ -30063,7 +30710,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="s">
-        <v>266</v>
+        <v>412</v>
       </c>
       <c r="C390">
         <v>1107</v>
@@ -30137,7 +30784,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="s">
-        <v>267</v>
+        <v>413</v>
       </c>
       <c r="C391">
         <v>902</v>
@@ -30211,7 +30858,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>228</v>
+        <v>414</v>
       </c>
       <c r="C392">
         <v>967</v>
@@ -30285,7 +30932,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>228</v>
+        <v>415</v>
       </c>
       <c r="C393">
         <v>1090</v>
@@ -30359,7 +31006,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="s">
-        <v>228</v>
+        <v>416</v>
       </c>
       <c r="C394">
         <v>706</v>
@@ -30433,7 +31080,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="s">
-        <v>221</v>
+        <v>417</v>
       </c>
       <c r="C395">
         <v>886</v>
@@ -30507,7 +31154,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="s">
-        <v>237</v>
+        <v>418</v>
       </c>
       <c r="C396">
         <v>811</v>
@@ -30581,7 +31228,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="s">
-        <v>268</v>
+        <v>419</v>
       </c>
       <c r="C397">
         <v>750</v>
@@ -30655,7 +31302,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="s">
-        <v>269</v>
+        <v>420</v>
       </c>
       <c r="C398">
         <v>896</v>
@@ -30729,7 +31376,7 @@
         <v>397</v>
       </c>
       <c r="B399" t="s">
-        <v>270</v>
+        <v>421</v>
       </c>
       <c r="C399">
         <v>749</v>
@@ -30803,7 +31450,7 @@
         <v>398</v>
       </c>
       <c r="B400" t="s">
-        <v>271</v>
+        <v>422</v>
       </c>
       <c r="C400">
         <v>1145</v>
@@ -30877,7 +31524,7 @@
         <v>399</v>
       </c>
       <c r="B401" t="s">
-        <v>111</v>
+        <v>423</v>
       </c>
       <c r="C401">
         <v>645</v>
@@ -30951,7 +31598,7 @@
         <v>400</v>
       </c>
       <c r="B402" t="s">
-        <v>112</v>
+        <v>424</v>
       </c>
       <c r="C402">
         <v>649</v>
@@ -31025,7 +31672,7 @@
         <v>401</v>
       </c>
       <c r="B403" t="s">
-        <v>272</v>
+        <v>425</v>
       </c>
       <c r="C403">
         <v>531</v>
@@ -31099,7 +31746,7 @@
         <v>402</v>
       </c>
       <c r="B404" t="s">
-        <v>273</v>
+        <v>426</v>
       </c>
       <c r="C404">
         <v>901</v>
@@ -31173,7 +31820,7 @@
         <v>403</v>
       </c>
       <c r="B405" t="s">
-        <v>274</v>
+        <v>427</v>
       </c>
       <c r="C405">
         <v>978</v>
@@ -31247,7 +31894,7 @@
         <v>404</v>
       </c>
       <c r="B406" t="s">
-        <v>275</v>
+        <v>428</v>
       </c>
       <c r="C406">
         <v>985</v>
@@ -31321,7 +31968,7 @@
         <v>405</v>
       </c>
       <c r="B407" t="s">
-        <v>276</v>
+        <v>429</v>
       </c>
       <c r="C407">
         <v>1175</v>
@@ -31395,7 +32042,7 @@
         <v>406</v>
       </c>
       <c r="B408" t="s">
-        <v>277</v>
+        <v>430</v>
       </c>
       <c r="C408">
         <v>994</v>
@@ -31469,7 +32116,7 @@
         <v>407</v>
       </c>
       <c r="B409" t="s">
-        <v>278</v>
+        <v>431</v>
       </c>
       <c r="C409">
         <v>1181</v>
@@ -31543,7 +32190,7 @@
         <v>408</v>
       </c>
       <c r="B410" t="s">
-        <v>279</v>
+        <v>432</v>
       </c>
       <c r="C410">
         <v>1180</v>
@@ -31617,7 +32264,7 @@
         <v>409</v>
       </c>
       <c r="B411" t="s">
-        <v>126</v>
+        <v>433</v>
       </c>
       <c r="C411">
         <v>901</v>
@@ -31691,7 +32338,7 @@
         <v>410</v>
       </c>
       <c r="B412" t="s">
-        <v>280</v>
+        <v>434</v>
       </c>
       <c r="C412">
         <v>925</v>
@@ -31765,7 +32412,7 @@
         <v>411</v>
       </c>
       <c r="B413" t="s">
-        <v>281</v>
+        <v>435</v>
       </c>
       <c r="C413">
         <v>1097</v>
@@ -31839,7 +32486,7 @@
         <v>412</v>
       </c>
       <c r="B414" t="s">
-        <v>229</v>
+        <v>436</v>
       </c>
       <c r="C414">
         <v>1005</v>
@@ -31913,7 +32560,7 @@
         <v>413</v>
       </c>
       <c r="B415" t="s">
-        <v>282</v>
+        <v>437</v>
       </c>
       <c r="C415">
         <v>1080</v>
@@ -31987,7 +32634,7 @@
         <v>414</v>
       </c>
       <c r="B416" t="s">
-        <v>283</v>
+        <v>438</v>
       </c>
       <c r="C416">
         <v>329</v>
@@ -32061,7 +32708,7 @@
         <v>415</v>
       </c>
       <c r="B417" t="s">
-        <v>284</v>
+        <v>439</v>
       </c>
       <c r="C417">
         <v>975</v>
@@ -32135,7 +32782,7 @@
         <v>416</v>
       </c>
       <c r="B418" t="s">
-        <v>184</v>
+        <v>440</v>
       </c>
       <c r="C418">
         <v>790</v>
@@ -32209,7 +32856,7 @@
         <v>417</v>
       </c>
       <c r="B419" t="s">
-        <v>199</v>
+        <v>441</v>
       </c>
       <c r="C419">
         <v>1187</v>
@@ -32283,7 +32930,7 @@
         <v>418</v>
       </c>
       <c r="B420" t="s">
-        <v>156</v>
+        <v>442</v>
       </c>
       <c r="C420">
         <v>801</v>
@@ -32357,7 +33004,7 @@
         <v>419</v>
       </c>
       <c r="B421" t="s">
-        <v>233</v>
+        <v>443</v>
       </c>
       <c r="C421">
         <v>935</v>
@@ -32431,7 +33078,7 @@
         <v>420</v>
       </c>
       <c r="B422" t="s">
-        <v>285</v>
+        <v>444</v>
       </c>
       <c r="C422">
         <v>729</v>
@@ -32505,7 +33152,7 @@
         <v>421</v>
       </c>
       <c r="B423" t="s">
-        <v>286</v>
+        <v>445</v>
       </c>
       <c r="C423">
         <v>964</v>
@@ -32579,7 +33226,7 @@
         <v>422</v>
       </c>
       <c r="B424" t="s">
-        <v>228</v>
+        <v>446</v>
       </c>
       <c r="C424">
         <v>611</v>
@@ -32653,7 +33300,7 @@
         <v>423</v>
       </c>
       <c r="B425" t="s">
-        <v>185</v>
+        <v>447</v>
       </c>
       <c r="C425">
         <v>1136</v>
@@ -32727,7 +33374,7 @@
         <v>424</v>
       </c>
       <c r="B426" t="s">
-        <v>287</v>
+        <v>448</v>
       </c>
       <c r="C426">
         <v>628</v>
@@ -32801,7 +33448,7 @@
         <v>425</v>
       </c>
       <c r="B427" t="s">
-        <v>184</v>
+        <v>449</v>
       </c>
       <c r="C427">
         <v>1181</v>
@@ -32875,7 +33522,7 @@
         <v>426</v>
       </c>
       <c r="B428" t="s">
-        <v>228</v>
+        <v>450</v>
       </c>
       <c r="C428">
         <v>643</v>
@@ -32949,7 +33596,7 @@
         <v>427</v>
       </c>
       <c r="B429" t="s">
-        <v>185</v>
+        <v>451</v>
       </c>
       <c r="C429">
         <v>651</v>
@@ -33023,7 +33670,7 @@
         <v>428</v>
       </c>
       <c r="B430" t="s">
-        <v>288</v>
+        <v>452</v>
       </c>
       <c r="C430">
         <v>822</v>
@@ -33097,7 +33744,7 @@
         <v>429</v>
       </c>
       <c r="B431" t="s">
-        <v>229</v>
+        <v>453</v>
       </c>
       <c r="C431">
         <v>1132</v>
@@ -33171,7 +33818,7 @@
         <v>430</v>
       </c>
       <c r="B432" t="s">
-        <v>184</v>
+        <v>454</v>
       </c>
       <c r="C432">
         <v>451</v>
@@ -33245,7 +33892,7 @@
         <v>431</v>
       </c>
       <c r="B433" t="s">
-        <v>233</v>
+        <v>455</v>
       </c>
       <c r="C433">
         <v>458</v>
@@ -33319,7 +33966,7 @@
         <v>432</v>
       </c>
       <c r="B434" t="s">
-        <v>229</v>
+        <v>456</v>
       </c>
       <c r="C434">
         <v>1106</v>
@@ -33393,7 +34040,7 @@
         <v>433</v>
       </c>
       <c r="B435" t="s">
-        <v>230</v>
+        <v>457</v>
       </c>
       <c r="C435">
         <v>1019</v>
@@ -33467,7 +34114,7 @@
         <v>434</v>
       </c>
       <c r="B436" t="s">
-        <v>289</v>
+        <v>458</v>
       </c>
       <c r="C436">
         <v>725</v>
@@ -33541,7 +34188,7 @@
         <v>435</v>
       </c>
       <c r="B437" t="s">
-        <v>290</v>
+        <v>459</v>
       </c>
       <c r="C437">
         <v>939</v>
@@ -33615,7 +34262,7 @@
         <v>436</v>
       </c>
       <c r="B438" t="s">
-        <v>291</v>
+        <v>460</v>
       </c>
       <c r="C438">
         <v>806</v>
@@ -33689,7 +34336,7 @@
         <v>437</v>
       </c>
       <c r="B439" t="s">
-        <v>292</v>
+        <v>461</v>
       </c>
       <c r="C439">
         <v>877</v>
@@ -33763,7 +34410,7 @@
         <v>438</v>
       </c>
       <c r="B440" t="s">
-        <v>293</v>
+        <v>462</v>
       </c>
       <c r="C440">
         <v>742</v>
@@ -33837,7 +34484,7 @@
         <v>439</v>
       </c>
       <c r="B441" t="s">
-        <v>233</v>
+        <v>463</v>
       </c>
       <c r="C441">
         <v>237</v>
@@ -33911,7 +34558,7 @@
         <v>440</v>
       </c>
       <c r="B442" t="s">
-        <v>233</v>
+        <v>464</v>
       </c>
       <c r="C442">
         <v>874</v>
@@ -33985,7 +34632,7 @@
         <v>441</v>
       </c>
       <c r="B443" t="s">
-        <v>139</v>
+        <v>465</v>
       </c>
       <c r="C443">
         <v>890</v>
@@ -34059,7 +34706,7 @@
         <v>442</v>
       </c>
       <c r="B444" t="s">
-        <v>292</v>
+        <v>466</v>
       </c>
       <c r="C444">
         <v>605</v>
@@ -34133,7 +34780,7 @@
         <v>443</v>
       </c>
       <c r="B445" t="s">
-        <v>294</v>
+        <v>467</v>
       </c>
       <c r="C445">
         <v>879</v>
@@ -34207,7 +34854,7 @@
         <v>444</v>
       </c>
       <c r="B446" t="s">
-        <v>295</v>
+        <v>468</v>
       </c>
       <c r="C446">
         <v>1009</v>
@@ -34281,7 +34928,7 @@
         <v>445</v>
       </c>
       <c r="B447" t="s">
-        <v>228</v>
+        <v>469</v>
       </c>
       <c r="C447">
         <v>646</v>
@@ -34355,7 +35002,7 @@
         <v>446</v>
       </c>
       <c r="B448" t="s">
-        <v>296</v>
+        <v>470</v>
       </c>
       <c r="C448">
         <v>1122</v>
@@ -34429,7 +35076,7 @@
         <v>447</v>
       </c>
       <c r="B449" t="s">
-        <v>282</v>
+        <v>471</v>
       </c>
       <c r="C449">
         <v>966</v>
@@ -34503,7 +35150,7 @@
         <v>448</v>
       </c>
       <c r="B450" t="s">
-        <v>297</v>
+        <v>472</v>
       </c>
       <c r="C450">
         <v>693</v>
@@ -34577,7 +35224,7 @@
         <v>449</v>
       </c>
       <c r="B451" t="s">
-        <v>297</v>
+        <v>473</v>
       </c>
       <c r="C451">
         <v>459</v>
@@ -34651,7 +35298,7 @@
         <v>450</v>
       </c>
       <c r="B452" t="s">
-        <v>228</v>
+        <v>474</v>
       </c>
       <c r="C452">
         <v>746</v>
@@ -34725,7 +35372,7 @@
         <v>451</v>
       </c>
       <c r="B453" t="s">
-        <v>185</v>
+        <v>475</v>
       </c>
       <c r="C453">
         <v>746</v>
@@ -34799,7 +35446,7 @@
         <v>452</v>
       </c>
       <c r="B454" t="s">
-        <v>298</v>
+        <v>476</v>
       </c>
       <c r="C454">
         <v>986</v>
@@ -34873,7 +35520,7 @@
         <v>453</v>
       </c>
       <c r="B455" t="s">
-        <v>299</v>
+        <v>477</v>
       </c>
       <c r="C455">
         <v>913</v>
@@ -34947,7 +35594,7 @@
         <v>454</v>
       </c>
       <c r="B456" t="s">
-        <v>300</v>
+        <v>478</v>
       </c>
       <c r="C456">
         <v>668</v>
@@ -35021,7 +35668,7 @@
         <v>455</v>
       </c>
       <c r="B457" t="s">
-        <v>301</v>
+        <v>479</v>
       </c>
       <c r="C457">
         <v>663</v>
@@ -35095,7 +35742,7 @@
         <v>456</v>
       </c>
       <c r="B458" t="s">
-        <v>297</v>
+        <v>480</v>
       </c>
       <c r="C458">
         <v>773</v>
@@ -35169,7 +35816,7 @@
         <v>457</v>
       </c>
       <c r="B459" t="s">
-        <v>302</v>
+        <v>481</v>
       </c>
       <c r="C459">
         <v>727</v>
@@ -35243,7 +35890,7 @@
         <v>458</v>
       </c>
       <c r="B460" t="s">
-        <v>303</v>
+        <v>482</v>
       </c>
       <c r="C460">
         <v>728</v>
@@ -35317,7 +35964,7 @@
         <v>459</v>
       </c>
       <c r="B461" t="s">
-        <v>304</v>
+        <v>483</v>
       </c>
       <c r="C461">
         <v>932</v>
@@ -35391,7 +36038,7 @@
         <v>460</v>
       </c>
       <c r="B462" t="s">
-        <v>297</v>
+        <v>484</v>
       </c>
       <c r="C462">
         <v>1000</v>
@@ -35465,7 +36112,7 @@
         <v>461</v>
       </c>
       <c r="B463" t="s">
-        <v>233</v>
+        <v>485</v>
       </c>
       <c r="C463">
         <v>997</v>
@@ -35539,7 +36186,7 @@
         <v>462</v>
       </c>
       <c r="B464" t="s">
-        <v>305</v>
+        <v>486</v>
       </c>
       <c r="C464">
         <v>728</v>
@@ -35613,7 +36260,7 @@
         <v>463</v>
       </c>
       <c r="B465" t="s">
-        <v>306</v>
+        <v>487</v>
       </c>
       <c r="C465">
         <v>520</v>
@@ -35687,7 +36334,7 @@
         <v>464</v>
       </c>
       <c r="B466" t="s">
-        <v>184</v>
+        <v>488</v>
       </c>
       <c r="C466">
         <v>882</v>
@@ -35761,7 +36408,7 @@
         <v>465</v>
       </c>
       <c r="B467" t="s">
-        <v>184</v>
+        <v>489</v>
       </c>
       <c r="C467">
         <v>1171</v>
@@ -35835,7 +36482,7 @@
         <v>466</v>
       </c>
       <c r="B468" t="s">
-        <v>199</v>
+        <v>490</v>
       </c>
       <c r="C468">
         <v>962</v>
@@ -35909,7 +36556,7 @@
         <v>467</v>
       </c>
       <c r="B469" t="s">
-        <v>307</v>
+        <v>491</v>
       </c>
       <c r="C469">
         <v>605</v>
@@ -35983,7 +36630,7 @@
         <v>468</v>
       </c>
       <c r="B470" t="s">
-        <v>308</v>
+        <v>492</v>
       </c>
       <c r="C470">
         <v>701</v>
